--- a/research/traditional_assets/database/data/greece/greece_transportation.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_transportation.xlsx
@@ -1127,7 +1127,7 @@
         <v>0.892</v>
       </c>
       <c r="F2">
-        <v>4.6179090482888</v>
+        <v>4.61790904828879</v>
       </c>
       <c r="G2">
         <v>9.859154929577469</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1087039974486549</v>
+        <v>0.1084999486542679</v>
       </c>
       <c r="C2">
-        <v>51.51878386750807</v>
+        <v>51.18042443794489</v>
       </c>
       <c r="D2">
-        <v>49.66878386750807</v>
+        <v>49.83042443794489</v>
       </c>
       <c r="E2">
-        <v>-35</v>
+        <v>-34.5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
         <v>1.85</v>
@@ -1445,28 +1445,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02515</v>
       </c>
       <c r="N2">
-        <v>4.596666666666668</v>
+        <v>4.571516666666668</v>
       </c>
       <c r="O2">
-        <v>1.011266666666667</v>
+        <v>1.005733666666667</v>
       </c>
       <c r="P2">
-        <v>3.585400000000001</v>
+        <v>3.565783000000001</v>
       </c>
       <c r="Q2">
-        <v>4.9054</v>
+        <v>4.885783</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1087039974486549</v>
+        <v>0.1091996047012807</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185858</v>
+        <v>0.826309383845217</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>182.7700463883367</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1084999486542679</v>
+        <v>0.1082958998598808</v>
       </c>
       <c r="C3">
-        <v>51.18042443794489</v>
+        <v>50.84312051965833</v>
       </c>
       <c r="D3">
-        <v>49.83042443794489</v>
+        <v>49.99312051965833</v>
       </c>
       <c r="E3">
-        <v>-34.5</v>
+        <v>-34</v>
       </c>
       <c r="F3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1.85</v>
@@ -1527,28 +1527,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M3">
-        <v>0.02515</v>
+        <v>0.0503</v>
       </c>
       <c r="N3">
-        <v>4.571516666666668</v>
+        <v>4.546366666666668</v>
       </c>
       <c r="O3">
-        <v>1.005733666666667</v>
+        <v>1.000200666666667</v>
       </c>
       <c r="P3">
-        <v>3.565783000000001</v>
+        <v>3.546166</v>
       </c>
       <c r="Q3">
-        <v>4.885783</v>
+        <v>4.866166</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1091996047012807</v>
+        <v>0.1097053263876335</v>
       </c>
       <c r="T3">
-        <v>0.826309383845217</v>
+        <v>0.8329006327499429</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>182.7700463883367</v>
+        <v>91.38502319416834</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1082958998598808</v>
+        <v>0.1080918510654938</v>
       </c>
       <c r="C4">
-        <v>50.84312051965833</v>
+        <v>50.5068824852316</v>
       </c>
       <c r="D4">
-        <v>49.99312051965833</v>
+        <v>50.1568824852316</v>
       </c>
       <c r="E4">
-        <v>-34</v>
+        <v>-33.5</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
         <v>1.85</v>
@@ -1609,28 +1609,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M4">
-        <v>0.0503</v>
+        <v>0.07544999999999999</v>
       </c>
       <c r="N4">
-        <v>4.546366666666668</v>
+        <v>4.521216666666668</v>
       </c>
       <c r="O4">
-        <v>1.000200666666667</v>
+        <v>0.9946676666666668</v>
       </c>
       <c r="P4">
-        <v>3.546166</v>
+        <v>3.526549000000001</v>
       </c>
       <c r="Q4">
-        <v>4.866166</v>
+        <v>4.846549</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1097053263876335</v>
+        <v>0.1102214753252513</v>
       </c>
       <c r="T4">
-        <v>0.8329006327499429</v>
+        <v>0.8396277836939413</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>91.38502319416834</v>
+        <v>60.92334879611224</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1080918510654938</v>
+        <v>0.1078878022711068</v>
       </c>
       <c r="C5">
-        <v>50.5068824852316</v>
+        <v>50.17172084360406</v>
       </c>
       <c r="D5">
-        <v>50.1568824852316</v>
+        <v>50.32172084360406</v>
       </c>
       <c r="E5">
-        <v>-33.5</v>
+        <v>-33</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>1.85</v>
@@ -1691,28 +1691,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M5">
-        <v>0.07544999999999999</v>
+        <v>0.1006</v>
       </c>
       <c r="N5">
-        <v>4.521216666666668</v>
+        <v>4.496066666666668</v>
       </c>
       <c r="O5">
-        <v>0.9946676666666668</v>
+        <v>0.9891346666666668</v>
       </c>
       <c r="P5">
-        <v>3.526549000000001</v>
+        <v>3.506932000000001</v>
       </c>
       <c r="Q5">
-        <v>4.846549</v>
+        <v>4.826932000000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1102214753252513</v>
+        <v>0.1107483773657362</v>
       </c>
       <c r="T5">
-        <v>0.8396277836939413</v>
+        <v>0.8464950836159398</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.92334879611224</v>
+        <v>45.69251159708417</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1078878022711068</v>
+        <v>0.1076837534767197</v>
       </c>
       <c r="C6">
-        <v>50.17172084360406</v>
+        <v>49.83764624231928</v>
       </c>
       <c r="D6">
-        <v>50.32172084360406</v>
+        <v>50.48764624231928</v>
       </c>
       <c r="E6">
-        <v>-33</v>
+        <v>-32.5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
         <v>1.85</v>
@@ -1773,28 +1773,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M6">
-        <v>0.1006</v>
+        <v>0.12575</v>
       </c>
       <c r="N6">
-        <v>4.496066666666668</v>
+        <v>4.470916666666668</v>
       </c>
       <c r="O6">
-        <v>0.9891346666666668</v>
+        <v>0.9836016666666668</v>
       </c>
       <c r="P6">
-        <v>3.506932000000001</v>
+        <v>3.487315000000001</v>
       </c>
       <c r="Q6">
-        <v>4.826932000000001</v>
+        <v>4.807315000000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1107483773657362</v>
+        <v>0.1112863720807576</v>
       </c>
       <c r="T6">
-        <v>0.8464950836159398</v>
+        <v>0.8535069582731383</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.69251159708417</v>
+        <v>36.55400927766733</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1076837534767197</v>
+        <v>0.1074797046823327</v>
       </c>
       <c r="C7">
-        <v>49.83764624231928</v>
+        <v>49.50466946981759</v>
       </c>
       <c r="D7">
-        <v>50.48764624231928</v>
+        <v>50.65466946981758</v>
       </c>
       <c r="E7">
-        <v>-32.5</v>
+        <v>-32</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>1.85</v>
@@ -1855,28 +1855,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M7">
-        <v>0.12575</v>
+        <v>0.1509</v>
       </c>
       <c r="N7">
-        <v>4.470916666666668</v>
+        <v>4.445766666666668</v>
       </c>
       <c r="O7">
-        <v>0.9836016666666668</v>
+        <v>0.9780686666666668</v>
       </c>
       <c r="P7">
-        <v>3.487315000000001</v>
+        <v>3.467698000000001</v>
       </c>
       <c r="Q7">
-        <v>4.807315000000001</v>
+        <v>4.787698000000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1112863720807576</v>
+        <v>0.1118358134918433</v>
       </c>
       <c r="T7">
-        <v>0.8535069582731383</v>
+        <v>0.8606680217528302</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.55400927766733</v>
+        <v>30.46167439805611</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1074797046823327</v>
+        <v>0.1072756558879456</v>
       </c>
       <c r="C8">
-        <v>49.50466946981759</v>
+        <v>49.17280145777441</v>
       </c>
       <c r="D8">
-        <v>50.65466946981758</v>
+        <v>50.82280145777441</v>
       </c>
       <c r="E8">
-        <v>-32</v>
+        <v>-31.5</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
         <v>1.85</v>
@@ -1937,28 +1937,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M8">
-        <v>0.1509</v>
+        <v>0.17605</v>
       </c>
       <c r="N8">
-        <v>4.445766666666668</v>
+        <v>4.420616666666668</v>
       </c>
       <c r="O8">
-        <v>0.9780686666666668</v>
+        <v>0.9725356666666669</v>
       </c>
       <c r="P8">
-        <v>3.467698000000001</v>
+        <v>3.448081000000001</v>
       </c>
       <c r="Q8">
-        <v>4.787698000000001</v>
+        <v>4.768081</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1118358134918433</v>
+        <v>0.1123970708472534</v>
       </c>
       <c r="T8">
-        <v>0.8606680217528302</v>
+        <v>0.8679830865976769</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.46167439805612</v>
+        <v>26.11000662690525</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1072756558879457</v>
+        <v>0.1070716070935586</v>
       </c>
       <c r="C9">
-        <v>49.17280145777439</v>
+        <v>48.84205328348538</v>
       </c>
       <c r="D9">
-        <v>50.82280145777439</v>
+        <v>50.99205328348538</v>
       </c>
       <c r="E9">
-        <v>-31.5</v>
+        <v>-31</v>
       </c>
       <c r="F9">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G9">
         <v>1.85</v>
@@ -2019,28 +2019,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M9">
-        <v>0.17605</v>
+        <v>0.2012</v>
       </c>
       <c r="N9">
-        <v>4.420616666666668</v>
+        <v>4.395466666666668</v>
       </c>
       <c r="O9">
-        <v>0.9725356666666669</v>
+        <v>0.9670026666666669</v>
       </c>
       <c r="P9">
-        <v>3.448081000000001</v>
+        <v>3.428464000000001</v>
       </c>
       <c r="Q9">
-        <v>4.768081</v>
+        <v>4.748464</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1123970708472534</v>
+        <v>0.1129705294495202</v>
       </c>
       <c r="T9">
-        <v>0.8679830865976771</v>
+        <v>0.8754571745913247</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.11000662690524</v>
+        <v>22.84625579854209</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1070716070935586</v>
+        <v>0.1068675582991716</v>
       </c>
       <c r="C10">
-        <v>48.84205328348538</v>
+        <v>48.51243617229913</v>
       </c>
       <c r="D10">
-        <v>50.99205328348538</v>
+        <v>51.16243617229912</v>
       </c>
       <c r="E10">
-        <v>-31</v>
+        <v>-30.5</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G10">
         <v>1.85</v>
@@ -2101,28 +2101,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M10">
-        <v>0.2012</v>
+        <v>0.22635</v>
       </c>
       <c r="N10">
-        <v>4.395466666666668</v>
+        <v>4.370316666666668</v>
       </c>
       <c r="O10">
-        <v>0.9670026666666669</v>
+        <v>0.9614696666666669</v>
       </c>
       <c r="P10">
-        <v>3.428464000000001</v>
+        <v>3.408847000000001</v>
       </c>
       <c r="Q10">
-        <v>4.748464</v>
+        <v>4.728847</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1129705294495202</v>
+        <v>0.1135565915375512</v>
       </c>
       <c r="T10">
-        <v>0.8754571745913247</v>
+        <v>0.8830955282551625</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.84625579854209</v>
+        <v>20.30778293203741</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1068675582991716</v>
+        <v>0.1066635095047845</v>
       </c>
       <c r="C11">
-        <v>48.51243617229913</v>
+        <v>48.18396150009905</v>
       </c>
       <c r="D11">
-        <v>51.16243617229912</v>
+        <v>51.33396150009905</v>
       </c>
       <c r="E11">
-        <v>-30.5</v>
+        <v>-30</v>
       </c>
       <c r="F11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>1.85</v>
@@ -2183,28 +2183,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M11">
-        <v>0.22635</v>
+        <v>0.2515</v>
       </c>
       <c r="N11">
-        <v>4.370316666666668</v>
+        <v>4.345166666666668</v>
       </c>
       <c r="O11">
-        <v>0.9614696666666669</v>
+        <v>0.9559366666666669</v>
       </c>
       <c r="P11">
-        <v>3.408847000000001</v>
+        <v>3.38923</v>
       </c>
       <c r="Q11">
-        <v>4.728847</v>
+        <v>4.70923</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1135565915375512</v>
+        <v>0.1141556772275384</v>
       </c>
       <c r="T11">
-        <v>0.8830955282551625</v>
+        <v>0.8909036231115299</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.30778293203741</v>
+        <v>18.27700463883367</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1066635095047845</v>
+        <v>0.1064594607103975</v>
       </c>
       <c r="C12">
-        <v>48.18396150009905</v>
+        <v>47.8566407958352</v>
       </c>
       <c r="D12">
-        <v>51.33396150009905</v>
+        <v>51.5066407958352</v>
       </c>
       <c r="E12">
-        <v>-30</v>
+        <v>-29.5</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G12">
         <v>1.85</v>
@@ -2265,28 +2265,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M12">
-        <v>0.2515</v>
+        <v>0.27665</v>
       </c>
       <c r="N12">
-        <v>4.345166666666668</v>
+        <v>4.320016666666668</v>
       </c>
       <c r="O12">
-        <v>0.9559366666666669</v>
+        <v>0.9504036666666669</v>
       </c>
       <c r="P12">
-        <v>3.38923</v>
+        <v>3.369613000000001</v>
       </c>
       <c r="Q12">
-        <v>4.70923</v>
+        <v>4.689613</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1141556772275384</v>
+        <v>0.1147682255173005</v>
       </c>
       <c r="T12">
-        <v>0.8909036231115299</v>
+        <v>0.8988871807736585</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.27700463883367</v>
+        <v>16.61545876257606</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1064594607103975</v>
+        <v>0.1062554119160105</v>
       </c>
       <c r="C13">
-        <v>47.8566407958352</v>
+        <v>47.53048574410742</v>
       </c>
       <c r="D13">
-        <v>51.5066407958352</v>
+        <v>51.68048574410742</v>
       </c>
       <c r="E13">
-        <v>-29.5</v>
+        <v>-29</v>
       </c>
       <c r="F13">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>1.85</v>
@@ -2347,28 +2347,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M13">
-        <v>0.27665</v>
+        <v>0.3018</v>
       </c>
       <c r="N13">
-        <v>4.320016666666668</v>
+        <v>4.294866666666667</v>
       </c>
       <c r="O13">
-        <v>0.9504036666666669</v>
+        <v>0.9448706666666669</v>
       </c>
       <c r="P13">
-        <v>3.369613000000001</v>
+        <v>3.349996000000001</v>
       </c>
       <c r="Q13">
-        <v>4.689613</v>
+        <v>4.669996000000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1147682255173005</v>
+        <v>0.1153946953591028</v>
       </c>
       <c r="T13">
-        <v>0.8988871807736585</v>
+        <v>0.9070521829281082</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.61545876257606</v>
+        <v>15.23083719902806</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1062554119160105</v>
+        <v>0.1060513631216234</v>
       </c>
       <c r="C14">
-        <v>47.53048574410742</v>
+        <v>47.20550818780113</v>
       </c>
       <c r="D14">
-        <v>51.68048574410742</v>
+        <v>51.85550818780113</v>
       </c>
       <c r="E14">
-        <v>-29</v>
+        <v>-28.5</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G14">
         <v>1.85</v>
@@ -2429,28 +2429,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M14">
-        <v>0.3018</v>
+        <v>0.32695</v>
       </c>
       <c r="N14">
-        <v>4.294866666666667</v>
+        <v>4.269716666666667</v>
       </c>
       <c r="O14">
-        <v>0.9448706666666669</v>
+        <v>0.9393376666666668</v>
       </c>
       <c r="P14">
-        <v>3.349996000000001</v>
+        <v>3.330379000000001</v>
       </c>
       <c r="Q14">
-        <v>4.669996000000001</v>
+        <v>4.650379000000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1153946953591028</v>
+        <v>0.1160355668064637</v>
       </c>
       <c r="T14">
-        <v>0.9070521829281082</v>
+        <v>0.9154048862815106</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.23083719902806</v>
+        <v>14.05923433756436</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1060513631216234</v>
+        <v>0.1058473143272364</v>
       </c>
       <c r="C15">
-        <v>47.20550818780113</v>
+        <v>46.88172013077639</v>
       </c>
       <c r="D15">
-        <v>51.85550818780113</v>
+        <v>52.03172013077639</v>
       </c>
       <c r="E15">
-        <v>-28.5</v>
+        <v>-28</v>
       </c>
       <c r="F15">
-        <v>6.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="G15">
         <v>1.85</v>
@@ -2511,28 +2511,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M15">
-        <v>0.32695</v>
+        <v>0.3521</v>
       </c>
       <c r="N15">
-        <v>4.269716666666667</v>
+        <v>4.244566666666667</v>
       </c>
       <c r="O15">
-        <v>0.9393376666666668</v>
+        <v>0.9338046666666668</v>
       </c>
       <c r="P15">
-        <v>3.330379000000001</v>
+        <v>3.310762</v>
       </c>
       <c r="Q15">
-        <v>4.650379000000001</v>
+        <v>4.630762000000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1160355668064637</v>
+        <v>0.1166913422409725</v>
       </c>
       <c r="T15">
-        <v>0.9154048862815106</v>
+        <v>0.9239518385501085</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.05923433756436</v>
+        <v>13.05500331345262</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1058473143272364</v>
+        <v>0.1058187655328493</v>
       </c>
       <c r="C16">
-        <v>46.88172013077639</v>
+        <v>46.40646977143344</v>
       </c>
       <c r="D16">
-        <v>52.03172013077639</v>
+        <v>52.05646977143344</v>
       </c>
       <c r="E16">
-        <v>-28</v>
+        <v>-27.5</v>
       </c>
       <c r="F16">
-        <v>7.000000000000001</v>
+        <v>7.500000000000001</v>
       </c>
       <c r="G16">
         <v>1.85</v>
@@ -2593,45 +2593,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M16">
-        <v>0.3521</v>
+        <v>0.3885</v>
       </c>
       <c r="N16">
-        <v>4.244566666666667</v>
+        <v>4.208166666666668</v>
       </c>
       <c r="O16">
-        <v>0.9338046666666668</v>
+        <v>0.9257966666666669</v>
       </c>
       <c r="P16">
-        <v>3.310762</v>
+        <v>3.282370000000001</v>
       </c>
       <c r="Q16">
-        <v>4.630762000000001</v>
+        <v>4.602370000000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1166913422409725</v>
+        <v>0.1173625476857051</v>
       </c>
       <c r="T16">
-        <v>0.9239518385501085</v>
+        <v>0.9326998955779676</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.05500331345262</v>
+        <v>11.83183183183183</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1058187655328493</v>
+        <v>0.1056264167384623</v>
       </c>
       <c r="C17">
-        <v>46.40646977143344</v>
+        <v>46.07383729478608</v>
       </c>
       <c r="D17">
-        <v>52.05646977143344</v>
+        <v>52.22383729478608</v>
       </c>
       <c r="E17">
-        <v>-27.5</v>
+        <v>-27</v>
       </c>
       <c r="F17">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>1.85</v>
@@ -2675,28 +2675,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M17">
-        <v>0.3885</v>
+        <v>0.4144</v>
       </c>
       <c r="N17">
-        <v>4.208166666666668</v>
+        <v>4.182266666666668</v>
       </c>
       <c r="O17">
-        <v>0.9257966666666669</v>
+        <v>0.920098666666667</v>
       </c>
       <c r="P17">
-        <v>3.282370000000001</v>
+        <v>3.262168000000001</v>
       </c>
       <c r="Q17">
-        <v>4.602370000000001</v>
+        <v>4.582168000000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1173625476857051</v>
+        <v>0.1180497342124551</v>
       </c>
       <c r="T17">
-        <v>0.9326998955779676</v>
+        <v>0.9416562396779186</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.83183183183183</v>
+        <v>11.09234234234235</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1056264167384623</v>
+        <v>0.1054340679440752</v>
       </c>
       <c r="C18">
-        <v>46.07383729478608</v>
+        <v>45.74228450102628</v>
       </c>
       <c r="D18">
-        <v>52.22383729478608</v>
+        <v>52.39228450102628</v>
       </c>
       <c r="E18">
-        <v>-27</v>
+        <v>-26.5</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G18">
         <v>1.85</v>
@@ -2757,28 +2757,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M18">
-        <v>0.4144</v>
+        <v>0.4403</v>
       </c>
       <c r="N18">
-        <v>4.182266666666668</v>
+        <v>4.156366666666668</v>
       </c>
       <c r="O18">
-        <v>0.920098666666667</v>
+        <v>0.914400666666667</v>
       </c>
       <c r="P18">
-        <v>3.262168000000001</v>
+        <v>3.241966000000001</v>
       </c>
       <c r="Q18">
-        <v>4.582168000000001</v>
+        <v>4.561966000000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1180497342124551</v>
+        <v>0.1187534794506931</v>
       </c>
       <c r="T18">
-        <v>0.9416562396779186</v>
+        <v>0.9508283992983503</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.09234234234235</v>
+        <v>10.43985161632221</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1054340679440752</v>
+        <v>0.1052417191496882</v>
       </c>
       <c r="C19">
-        <v>45.74228450102628</v>
+        <v>45.41182187146433</v>
       </c>
       <c r="D19">
-        <v>52.39228450102628</v>
+        <v>52.56182187146433</v>
       </c>
       <c r="E19">
-        <v>-26.5</v>
+        <v>-26</v>
       </c>
       <c r="F19">
-        <v>8.5</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="G19">
         <v>1.85</v>
@@ -2839,28 +2839,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M19">
-        <v>0.4403</v>
+        <v>0.4662000000000001</v>
       </c>
       <c r="N19">
-        <v>4.156366666666668</v>
+        <v>4.130466666666668</v>
       </c>
       <c r="O19">
-        <v>0.914400666666667</v>
+        <v>0.9087026666666669</v>
       </c>
       <c r="P19">
-        <v>3.241966000000001</v>
+        <v>3.221764000000001</v>
       </c>
       <c r="Q19">
-        <v>4.561966000000001</v>
+        <v>4.541764000000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1187534794506931</v>
+        <v>0.1194743892069368</v>
       </c>
       <c r="T19">
-        <v>0.9508283992983503</v>
+        <v>0.9602242701290364</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.43985161632221</v>
+        <v>9.859859859859862</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1052417191496882</v>
+        <v>0.1053013103553012</v>
       </c>
       <c r="C20">
-        <v>45.41182187146434</v>
+        <v>44.85918063859348</v>
       </c>
       <c r="D20">
-        <v>52.56182187146434</v>
+        <v>52.50918063859348</v>
       </c>
       <c r="E20">
-        <v>-26</v>
+        <v>-25.5</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G20">
         <v>1.85</v>
@@ -2921,45 +2921,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M20">
-        <v>0.4662</v>
+        <v>0.50825</v>
       </c>
       <c r="N20">
-        <v>4.130466666666668</v>
+        <v>4.088416666666667</v>
       </c>
       <c r="O20">
-        <v>0.9087026666666669</v>
+        <v>0.8994516666666668</v>
       </c>
       <c r="P20">
-        <v>3.221764000000001</v>
+        <v>3.188965</v>
       </c>
       <c r="Q20">
-        <v>4.541764000000001</v>
+        <v>4.508965</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1194743892069368</v>
+        <v>0.1202130992040755</v>
       </c>
       <c r="T20">
-        <v>0.9602242701290362</v>
+        <v>0.9698521377703567</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.859859859859862</v>
+        <v>9.044105591080507</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1053013103553012</v>
+        <v>0.1051222215609141</v>
       </c>
       <c r="C21">
-        <v>44.85918063859348</v>
+        <v>44.51770143581548</v>
       </c>
       <c r="D21">
-        <v>52.50918063859348</v>
+        <v>52.66770143581548</v>
       </c>
       <c r="E21">
-        <v>-25.5</v>
+        <v>-25</v>
       </c>
       <c r="F21">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1.85</v>
@@ -3003,28 +3003,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M21">
-        <v>0.50825</v>
+        <v>0.535</v>
       </c>
       <c r="N21">
-        <v>4.088416666666667</v>
+        <v>4.061666666666667</v>
       </c>
       <c r="O21">
-        <v>0.8994516666666668</v>
+        <v>0.8935666666666668</v>
       </c>
       <c r="P21">
-        <v>3.188965</v>
+        <v>3.168100000000001</v>
       </c>
       <c r="Q21">
-        <v>4.508965</v>
+        <v>4.488100000000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1202130992040755</v>
+        <v>0.1209702769511427</v>
       </c>
       <c r="T21">
-        <v>0.9698521377703567</v>
+        <v>0.97972070210271</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.044105591080507</v>
+        <v>8.59190031152648</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1051222215609141</v>
+        <v>0.1049431327665271</v>
       </c>
       <c r="C22">
-        <v>44.51770143581548</v>
+        <v>44.17718225314912</v>
       </c>
       <c r="D22">
-        <v>52.66770143581548</v>
+        <v>52.82718225314912</v>
       </c>
       <c r="E22">
-        <v>-25</v>
+        <v>-24.5</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G22">
         <v>1.85</v>
@@ -3085,28 +3085,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M22">
-        <v>0.535</v>
+        <v>0.5617500000000001</v>
       </c>
       <c r="N22">
-        <v>4.061666666666667</v>
+        <v>4.034916666666668</v>
       </c>
       <c r="O22">
-        <v>0.8935666666666668</v>
+        <v>0.8876816666666669</v>
       </c>
       <c r="P22">
-        <v>3.168100000000001</v>
+        <v>3.147235000000001</v>
       </c>
       <c r="Q22">
-        <v>4.488100000000001</v>
+        <v>4.467235000000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1209702769511427</v>
+        <v>0.1217466237550976</v>
       </c>
       <c r="T22">
-        <v>0.97972070210271</v>
+        <v>0.9898391035067686</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.59190031152648</v>
+        <v>8.182762201453791</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1049431327665271</v>
+        <v>0.10476404397214</v>
       </c>
       <c r="C23">
-        <v>44.17718225314912</v>
+        <v>43.8376318380699</v>
       </c>
       <c r="D23">
-        <v>52.82718225314912</v>
+        <v>52.9876318380699</v>
       </c>
       <c r="E23">
-        <v>-24.5</v>
+        <v>-24</v>
       </c>
       <c r="F23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1.85</v>
@@ -3167,28 +3167,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M23">
-        <v>0.56175</v>
+        <v>0.5885</v>
       </c>
       <c r="N23">
-        <v>4.034916666666668</v>
+        <v>4.008166666666668</v>
       </c>
       <c r="O23">
-        <v>0.8876816666666669</v>
+        <v>0.8817966666666669</v>
       </c>
       <c r="P23">
-        <v>3.147235000000001</v>
+        <v>3.126370000000001</v>
       </c>
       <c r="Q23">
-        <v>4.467235000000001</v>
+        <v>4.446370000000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1217466237550976</v>
+        <v>0.122542876887359</v>
       </c>
       <c r="T23">
-        <v>0.9898391035067684</v>
+        <v>1.000216951100675</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.182762201453793</v>
+        <v>7.810818465024074</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.10476404397214</v>
+        <v>0.104728475177753</v>
       </c>
       <c r="C24">
-        <v>43.8376318380699</v>
+        <v>43.36961478309299</v>
       </c>
       <c r="D24">
-        <v>52.9876318380699</v>
+        <v>53.01961478309299</v>
       </c>
       <c r="E24">
-        <v>-24</v>
+        <v>-23.5</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G24">
         <v>1.85</v>
@@ -3249,45 +3249,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M24">
-        <v>0.5885</v>
+        <v>0.6244500000000001</v>
       </c>
       <c r="N24">
-        <v>4.008166666666668</v>
+        <v>3.972216666666668</v>
       </c>
       <c r="O24">
-        <v>0.8817966666666669</v>
+        <v>0.8738876666666668</v>
       </c>
       <c r="P24">
-        <v>3.126370000000001</v>
+        <v>3.098329000000001</v>
       </c>
       <c r="Q24">
-        <v>4.446370000000001</v>
+        <v>4.418329</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.122542876887359</v>
+        <v>0.1233598119191597</v>
       </c>
       <c r="T24">
-        <v>1.000216951100675</v>
+        <v>1.010864353177539</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.810818465024074</v>
+        <v>7.361144473803614</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.104728475177753</v>
+        <v>0.1045556263833659</v>
       </c>
       <c r="C25">
-        <v>43.36961478309299</v>
+        <v>43.02558923283042</v>
       </c>
       <c r="D25">
-        <v>53.01961478309299</v>
+        <v>53.17558923283042</v>
       </c>
       <c r="E25">
-        <v>-23.5</v>
+        <v>-23</v>
       </c>
       <c r="F25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1.85</v>
@@ -3331,28 +3331,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M25">
-        <v>0.6244500000000001</v>
+        <v>0.6516000000000001</v>
       </c>
       <c r="N25">
-        <v>3.972216666666668</v>
+        <v>3.945066666666667</v>
       </c>
       <c r="O25">
-        <v>0.8738876666666668</v>
+        <v>0.8679146666666668</v>
       </c>
       <c r="P25">
-        <v>3.098329000000001</v>
+        <v>3.077152000000001</v>
       </c>
       <c r="Q25">
-        <v>4.418329</v>
+        <v>4.397152</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1233598119191597</v>
+        <v>0.124198245241271</v>
       </c>
       <c r="T25">
-        <v>1.010864353177539</v>
+        <v>1.021791950045901</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.361144473803614</v>
+        <v>7.054430120728464</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1045556263833659</v>
+        <v>0.1043827775889789</v>
       </c>
       <c r="C26">
-        <v>43.02558923283042</v>
+        <v>42.68248408944174</v>
       </c>
       <c r="D26">
-        <v>53.17558923283042</v>
+        <v>53.33248408944173</v>
       </c>
       <c r="E26">
-        <v>-23</v>
+        <v>-22.5</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G26">
         <v>1.85</v>
@@ -3413,28 +3413,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M26">
-        <v>0.6516</v>
+        <v>0.67875</v>
       </c>
       <c r="N26">
-        <v>3.945066666666667</v>
+        <v>3.917916666666668</v>
       </c>
       <c r="O26">
-        <v>0.8679146666666668</v>
+        <v>0.8619416666666668</v>
       </c>
       <c r="P26">
-        <v>3.077152000000001</v>
+        <v>3.055975000000001</v>
       </c>
       <c r="Q26">
-        <v>4.397152</v>
+        <v>4.375975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.124198245241271</v>
+        <v>0.1250590367853052</v>
       </c>
       <c r="T26">
-        <v>1.021791950045901</v>
+        <v>1.033010949497418</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.054430120728465</v>
+        <v>6.772252915899326</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1043827775889789</v>
+        <v>0.1042099287945919</v>
       </c>
       <c r="C27">
-        <v>42.68248408944174</v>
+        <v>42.34030752403184</v>
       </c>
       <c r="D27">
-        <v>53.33248408944173</v>
+        <v>53.49030752403184</v>
       </c>
       <c r="E27">
-        <v>-22.5</v>
+        <v>-22</v>
       </c>
       <c r="F27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1.85</v>
@@ -3495,28 +3495,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M27">
-        <v>0.67875</v>
+        <v>0.7059</v>
       </c>
       <c r="N27">
-        <v>3.917916666666668</v>
+        <v>3.890766666666668</v>
       </c>
       <c r="O27">
-        <v>0.8619416666666668</v>
+        <v>0.8559686666666669</v>
       </c>
       <c r="P27">
-        <v>3.055975000000001</v>
+        <v>3.034798000000001</v>
       </c>
       <c r="Q27">
-        <v>4.375975</v>
+        <v>4.354798000000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1250590367853052</v>
+        <v>0.1259430929656647</v>
       </c>
       <c r="T27">
-        <v>1.033010949497418</v>
+        <v>1.044533165150328</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.772252915899326</v>
+        <v>6.511781649903199</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1042099287945919</v>
+        <v>0.1040370800002048</v>
       </c>
       <c r="C28">
-        <v>42.34030752403184</v>
+        <v>41.99906780471365</v>
       </c>
       <c r="D28">
-        <v>53.49030752403184</v>
+        <v>53.64906780471365</v>
       </c>
       <c r="E28">
-        <v>-22</v>
+        <v>-21.5</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G28">
         <v>1.85</v>
@@ -3577,28 +3577,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M28">
-        <v>0.7059</v>
+        <v>0.73305</v>
       </c>
       <c r="N28">
-        <v>3.890766666666668</v>
+        <v>3.863616666666668</v>
       </c>
       <c r="O28">
-        <v>0.8559686666666669</v>
+        <v>0.8499956666666669</v>
       </c>
       <c r="P28">
-        <v>3.034798000000001</v>
+        <v>3.013621000000001</v>
       </c>
       <c r="Q28">
-        <v>4.354798000000001</v>
+        <v>4.333621000000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1259430929656647</v>
+        <v>0.1268513698632943</v>
       </c>
       <c r="T28">
-        <v>1.044533165150328</v>
+        <v>1.056371057944413</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.511781649903199</v>
+        <v>6.270604551758636</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1040370800002048</v>
+        <v>0.1040826312058178</v>
       </c>
       <c r="C29">
-        <v>41.99906780471365</v>
+        <v>41.4571379935854</v>
       </c>
       <c r="D29">
-        <v>53.64906780471365</v>
+        <v>53.6071379935854</v>
       </c>
       <c r="E29">
-        <v>-21.5</v>
+        <v>-21</v>
       </c>
       <c r="F29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1.85</v>
@@ -3659,45 +3659,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M29">
-        <v>0.73305</v>
+        <v>0.7742000000000001</v>
       </c>
       <c r="N29">
-        <v>3.863616666666668</v>
+        <v>3.822466666666668</v>
       </c>
       <c r="O29">
-        <v>0.8499956666666669</v>
+        <v>0.8409426666666668</v>
       </c>
       <c r="P29">
-        <v>3.013621000000001</v>
+        <v>2.981524000000001</v>
       </c>
       <c r="Q29">
-        <v>4.333621000000001</v>
+        <v>4.301524000000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1268513698632943</v>
+        <v>0.1277848766747469</v>
       </c>
       <c r="T29">
-        <v>1.056371057944413</v>
+        <v>1.06853778109389</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.270604551758636</v>
+        <v>5.937311633514166</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1040826312058178</v>
+        <v>0.1039175824114308</v>
       </c>
       <c r="C30">
-        <v>41.4571379935854</v>
+        <v>41.10937752470947</v>
       </c>
       <c r="D30">
-        <v>53.6071379935854</v>
+        <v>53.75937752470947</v>
       </c>
       <c r="E30">
-        <v>-21</v>
+        <v>-20.5</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G30">
         <v>1.85</v>
@@ -3741,28 +3741,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M30">
-        <v>0.7742000000000001</v>
+        <v>0.8018500000000002</v>
       </c>
       <c r="N30">
-        <v>3.822466666666668</v>
+        <v>3.794816666666668</v>
       </c>
       <c r="O30">
-        <v>0.8409426666666668</v>
+        <v>0.8348596666666669</v>
       </c>
       <c r="P30">
-        <v>2.981524000000001</v>
+        <v>2.959957000000001</v>
       </c>
       <c r="Q30">
-        <v>4.301524000000001</v>
+        <v>4.279957</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1277848766747469</v>
+        <v>0.1287446794527194</v>
       </c>
       <c r="T30">
-        <v>1.06853778109389</v>
+        <v>1.081047228839127</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.937311633514166</v>
+        <v>5.732576749599883</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1039175824114307</v>
+        <v>0.1037525336170437</v>
       </c>
       <c r="C31">
-        <v>41.10937752470949</v>
+        <v>40.76248421209067</v>
       </c>
       <c r="D31">
-        <v>53.75937752470949</v>
+        <v>53.91248421209067</v>
       </c>
       <c r="E31">
-        <v>-20.5</v>
+        <v>-20</v>
       </c>
       <c r="F31">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>1.85</v>
@@ -3823,28 +3823,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M31">
-        <v>0.80185</v>
+        <v>0.8295</v>
       </c>
       <c r="N31">
-        <v>3.794816666666668</v>
+        <v>3.767166666666668</v>
       </c>
       <c r="O31">
-        <v>0.8348596666666669</v>
+        <v>0.8287766666666669</v>
       </c>
       <c r="P31">
-        <v>2.959957000000001</v>
+        <v>2.938390000000001</v>
       </c>
       <c r="Q31">
-        <v>4.279957</v>
+        <v>4.25839</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1287446794527194</v>
+        <v>0.1297319051672053</v>
       </c>
       <c r="T31">
-        <v>1.081047228839127</v>
+        <v>1.093914089377084</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.732576749599885</v>
+        <v>5.541490857946555</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1037525336170437</v>
+        <v>0.1035874848226567</v>
       </c>
       <c r="C32">
-        <v>40.76248421209067</v>
+        <v>40.41646548587206</v>
       </c>
       <c r="D32">
-        <v>53.91248421209067</v>
+        <v>54.06646548587206</v>
       </c>
       <c r="E32">
-        <v>-20</v>
+        <v>-19.5</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G32">
         <v>1.85</v>
@@ -3905,28 +3905,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M32">
-        <v>0.8295</v>
+        <v>0.8571500000000001</v>
       </c>
       <c r="N32">
-        <v>3.767166666666668</v>
+        <v>3.739516666666668</v>
       </c>
       <c r="O32">
-        <v>0.8287766666666669</v>
+        <v>0.8226936666666669</v>
       </c>
       <c r="P32">
-        <v>2.938390000000001</v>
+        <v>2.916823000000001</v>
       </c>
       <c r="Q32">
-        <v>4.25839</v>
+        <v>4.236823000000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1297319051672053</v>
+        <v>0.1307477461197923</v>
       </c>
       <c r="T32">
-        <v>1.093914089377084</v>
+        <v>1.107153902394403</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.541490857946555</v>
+        <v>5.362733088335376</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1035874848226567</v>
+        <v>0.1034224360282696</v>
       </c>
       <c r="C33">
-        <v>40.41646548587206</v>
+        <v>40.07132886132591</v>
       </c>
       <c r="D33">
-        <v>54.06646548587206</v>
+        <v>54.22132886132591</v>
       </c>
       <c r="E33">
-        <v>-19.5</v>
+        <v>-19</v>
       </c>
       <c r="F33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G33">
         <v>1.85</v>
@@ -3987,28 +3987,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M33">
-        <v>0.8571500000000001</v>
+        <v>0.8848</v>
       </c>
       <c r="N33">
-        <v>3.739516666666668</v>
+        <v>3.711866666666667</v>
       </c>
       <c r="O33">
-        <v>0.8226936666666669</v>
+        <v>0.8166106666666668</v>
       </c>
       <c r="P33">
-        <v>2.916823000000001</v>
+        <v>2.895256000000001</v>
       </c>
       <c r="Q33">
-        <v>4.236823000000001</v>
+        <v>4.215256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1307477461197923</v>
+        <v>0.1317934647474553</v>
       </c>
       <c r="T33">
-        <v>1.107153902394403</v>
+        <v>1.120783121676937</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.362733088335376</v>
+        <v>5.195147679324895</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1034224360282696</v>
+        <v>0.1032573872338826</v>
       </c>
       <c r="C34">
-        <v>40.07132886132591</v>
+        <v>39.7270819400762</v>
       </c>
       <c r="D34">
-        <v>54.22132886132591</v>
+        <v>54.3770819400762</v>
       </c>
       <c r="E34">
-        <v>-19</v>
+        <v>-18.5</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G34">
         <v>1.85</v>
@@ -4069,28 +4069,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M34">
-        <v>0.8848</v>
+        <v>0.91245</v>
       </c>
       <c r="N34">
-        <v>3.711866666666667</v>
+        <v>3.684216666666668</v>
       </c>
       <c r="O34">
-        <v>0.8166106666666668</v>
+        <v>0.8105276666666669</v>
       </c>
       <c r="P34">
-        <v>2.895256000000001</v>
+        <v>2.873689000000001</v>
       </c>
       <c r="Q34">
-        <v>4.215256</v>
+        <v>4.193689000000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1317934647474553</v>
+        <v>0.1328703988565412</v>
       </c>
       <c r="T34">
-        <v>1.120783121676937</v>
+        <v>1.134819183326114</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.195147679324895</v>
+        <v>5.037718961769596</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1032573872338826</v>
+        <v>0.1030923384394955</v>
       </c>
       <c r="C35">
-        <v>39.7270819400762</v>
+        <v>39.38373241134249</v>
       </c>
       <c r="D35">
-        <v>54.3770819400762</v>
+        <v>54.53373241134249</v>
       </c>
       <c r="E35">
-        <v>-18.5</v>
+        <v>-18</v>
       </c>
       <c r="F35">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="G35">
         <v>1.85</v>
@@ -4151,28 +4151,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M35">
-        <v>0.91245</v>
+        <v>0.9401</v>
       </c>
       <c r="N35">
-        <v>3.684216666666668</v>
+        <v>3.656566666666667</v>
       </c>
       <c r="O35">
-        <v>0.8105276666666669</v>
+        <v>0.8044446666666668</v>
       </c>
       <c r="P35">
-        <v>2.873689000000001</v>
+        <v>2.852122</v>
       </c>
       <c r="Q35">
-        <v>4.193689000000001</v>
+        <v>4.172122</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1328703988565412</v>
+        <v>0.133979967332569</v>
       </c>
       <c r="T35">
-        <v>1.134819183326114</v>
+        <v>1.149280580176781</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.037718961769596</v>
+        <v>4.889550757011666</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1030923384394955</v>
+        <v>0.1029272896451085</v>
       </c>
       <c r="C36">
-        <v>39.38373241134249</v>
+        <v>39.0412880532053</v>
       </c>
       <c r="D36">
-        <v>54.53373241134249</v>
+        <v>54.6912880532053</v>
       </c>
       <c r="E36">
-        <v>-18</v>
+        <v>-17.5</v>
       </c>
       <c r="F36">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G36">
         <v>1.85</v>
@@ -4233,28 +4233,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M36">
-        <v>0.9401</v>
+        <v>0.96775</v>
       </c>
       <c r="N36">
-        <v>3.656566666666667</v>
+        <v>3.628916666666667</v>
       </c>
       <c r="O36">
-        <v>0.8044446666666668</v>
+        <v>0.7983616666666669</v>
       </c>
       <c r="P36">
-        <v>2.852122</v>
+        <v>2.830555</v>
       </c>
       <c r="Q36">
-        <v>4.172122</v>
+        <v>4.150555000000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.133979967332569</v>
+        <v>0.13512367637709</v>
       </c>
       <c r="T36">
-        <v>1.149280580176781</v>
+        <v>1.164186943084392</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.889550757011666</v>
+        <v>4.749849306811333</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1029272896451085</v>
+        <v>0.1027622408507215</v>
       </c>
       <c r="C37">
-        <v>39.0412880532053</v>
+        <v>38.69975673389348</v>
       </c>
       <c r="D37">
-        <v>54.6912880532053</v>
+        <v>54.84975673389348</v>
       </c>
       <c r="E37">
-        <v>-17.5</v>
+        <v>-17</v>
       </c>
       <c r="F37">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G37">
         <v>1.85</v>
@@ -4315,28 +4315,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M37">
-        <v>0.96775</v>
+        <v>0.9954000000000003</v>
       </c>
       <c r="N37">
-        <v>3.628916666666667</v>
+        <v>3.601266666666668</v>
       </c>
       <c r="O37">
-        <v>0.7983616666666669</v>
+        <v>0.7922786666666669</v>
       </c>
       <c r="P37">
-        <v>2.830555</v>
+        <v>2.808988000000001</v>
       </c>
       <c r="Q37">
-        <v>4.150555000000001</v>
+        <v>4.128988000000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.13512367637709</v>
+        <v>0.1363031263292523</v>
       </c>
       <c r="T37">
-        <v>1.164186943084392</v>
+        <v>1.179559129832865</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.749849306811333</v>
+        <v>4.617909048288794</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1027622408507215</v>
+        <v>0.1033186920563344</v>
       </c>
       <c r="C38">
-        <v>38.69975673389347</v>
+        <v>37.66912552217781</v>
       </c>
       <c r="D38">
-        <v>54.84975673389347</v>
+        <v>54.31912552217781</v>
       </c>
       <c r="E38">
-        <v>-17</v>
+        <v>-16.5</v>
       </c>
       <c r="F38">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G38">
         <v>1.85</v>
@@ -4397,45 +4397,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M38">
-        <v>0.9954000000000001</v>
+        <v>1.0693</v>
       </c>
       <c r="N38">
-        <v>3.601266666666668</v>
+        <v>3.527366666666667</v>
       </c>
       <c r="O38">
-        <v>0.7922786666666669</v>
+        <v>0.7760206666666668</v>
       </c>
       <c r="P38">
-        <v>2.808988000000001</v>
+        <v>2.751346000000001</v>
       </c>
       <c r="Q38">
-        <v>4.128988000000001</v>
+        <v>4.071346</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1363031263292523</v>
+        <v>0.1375200191370388</v>
       </c>
       <c r="T38">
-        <v>1.179559129832865</v>
+        <v>1.195419322509862</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.617909048288796</v>
+        <v>4.29876243025032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1033186920563344</v>
+        <v>0.1031731432619474</v>
       </c>
       <c r="C39">
-        <v>37.66912552217781</v>
+        <v>37.30692663925824</v>
       </c>
       <c r="D39">
-        <v>54.31912552217781</v>
+        <v>54.45692663925824</v>
       </c>
       <c r="E39">
-        <v>-16.5</v>
+        <v>-16</v>
       </c>
       <c r="F39">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="G39">
         <v>1.85</v>
@@ -4479,28 +4479,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M39">
-        <v>1.0693</v>
+        <v>1.0982</v>
       </c>
       <c r="N39">
-        <v>3.527366666666667</v>
+        <v>3.498466666666667</v>
       </c>
       <c r="O39">
-        <v>0.7760206666666668</v>
+        <v>0.7696626666666668</v>
       </c>
       <c r="P39">
-        <v>2.751346000000001</v>
+        <v>2.728804</v>
       </c>
       <c r="Q39">
-        <v>4.071346</v>
+        <v>4.048804000000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1375200191370388</v>
+        <v>0.138776166551528</v>
       </c>
       <c r="T39">
-        <v>1.195419322509862</v>
+        <v>1.211791134305471</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.29876243025032</v>
+        <v>4.18563710313847</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1031731432619474</v>
+        <v>0.1030275944675604</v>
       </c>
       <c r="C40">
-        <v>37.30692663925824</v>
+        <v>36.94542870442646</v>
       </c>
       <c r="D40">
-        <v>54.45692663925824</v>
+        <v>54.59542870442646</v>
       </c>
       <c r="E40">
-        <v>-16</v>
+        <v>-15.5</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G40">
         <v>1.85</v>
@@ -4561,28 +4561,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M40">
-        <v>1.0982</v>
+        <v>1.1271</v>
       </c>
       <c r="N40">
-        <v>3.498466666666667</v>
+        <v>3.469566666666668</v>
       </c>
       <c r="O40">
-        <v>0.7696626666666668</v>
+        <v>0.7633046666666669</v>
       </c>
       <c r="P40">
-        <v>2.728804</v>
+        <v>2.706262000000001</v>
       </c>
       <c r="Q40">
-        <v>4.048804000000001</v>
+        <v>4.026262000000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.138776166551528</v>
+        <v>0.1400734991271481</v>
       </c>
       <c r="T40">
-        <v>1.211791134305471</v>
+        <v>1.228699726815691</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.18563710313847</v>
+        <v>4.078313074852868</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1030275944675604</v>
+        <v>0.1039740456731733</v>
       </c>
       <c r="C41">
-        <v>36.94542870442646</v>
+        <v>35.55719910443341</v>
       </c>
       <c r="D41">
-        <v>54.59542870442646</v>
+        <v>53.70719910443341</v>
       </c>
       <c r="E41">
-        <v>-15.5</v>
+        <v>-15</v>
       </c>
       <c r="F41">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="G41">
         <v>1.85</v>
@@ -4643,45 +4643,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M41">
-        <v>1.1271</v>
+        <v>1.226</v>
       </c>
       <c r="N41">
-        <v>3.469566666666668</v>
+        <v>3.370666666666668</v>
       </c>
       <c r="O41">
-        <v>0.7633046666666669</v>
+        <v>0.7415466666666669</v>
       </c>
       <c r="P41">
-        <v>2.706262000000001</v>
+        <v>2.629120000000001</v>
       </c>
       <c r="Q41">
-        <v>4.026262000000001</v>
+        <v>3.949120000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1400734991271481</v>
+        <v>0.1414140761219555</v>
       </c>
       <c r="T41">
-        <v>1.228699726815691</v>
+        <v>1.24617193907625</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.078313074852868</v>
+        <v>3.749320282762372</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1039740456731733</v>
+        <v>0.1038557968787862</v>
       </c>
       <c r="C42">
-        <v>35.55719910443341</v>
+        <v>35.16659061889776</v>
       </c>
       <c r="D42">
-        <v>53.70719910443341</v>
+        <v>53.81659061889776</v>
       </c>
       <c r="E42">
-        <v>-15</v>
+        <v>-14.5</v>
       </c>
       <c r="F42">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="G42">
         <v>1.85</v>
@@ -4725,28 +4725,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M42">
-        <v>1.226</v>
+        <v>1.25665</v>
       </c>
       <c r="N42">
-        <v>3.370666666666668</v>
+        <v>3.340016666666668</v>
       </c>
       <c r="O42">
-        <v>0.7415466666666669</v>
+        <v>0.7348036666666669</v>
       </c>
       <c r="P42">
-        <v>2.629120000000001</v>
+        <v>2.605213000000001</v>
       </c>
       <c r="Q42">
-        <v>3.949120000000001</v>
+        <v>3.925213000000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1414140761219555</v>
+        <v>0.1428000964047225</v>
       </c>
       <c r="T42">
-        <v>1.24617193907625</v>
+        <v>1.264236429718524</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.749320282762372</v>
+        <v>3.657873446597435</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1038557968787862</v>
+        <v>0.1037375480843992</v>
       </c>
       <c r="C43">
-        <v>35.16659061889776</v>
+        <v>34.77642866294882</v>
       </c>
       <c r="D43">
-        <v>53.81659061889776</v>
+        <v>53.92642866294882</v>
       </c>
       <c r="E43">
-        <v>-14.5</v>
+        <v>-14</v>
       </c>
       <c r="F43">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="G43">
         <v>1.85</v>
@@ -4807,28 +4807,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M43">
-        <v>1.25665</v>
+        <v>1.2873</v>
       </c>
       <c r="N43">
-        <v>3.340016666666668</v>
+        <v>3.309366666666667</v>
       </c>
       <c r="O43">
-        <v>0.7348036666666669</v>
+        <v>0.7280606666666668</v>
       </c>
       <c r="P43">
-        <v>2.605213000000001</v>
+        <v>2.581306000000001</v>
       </c>
       <c r="Q43">
-        <v>3.925213000000001</v>
+        <v>3.901306</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1428000964047225</v>
+        <v>0.1442339104903435</v>
       </c>
       <c r="T43">
-        <v>1.264236429718524</v>
+        <v>1.282923833831221</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.657873446597435</v>
+        <v>3.570781221678448</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1037375480843992</v>
+        <v>0.1045584192900122</v>
       </c>
       <c r="C44">
-        <v>34.77642866294882</v>
+        <v>33.52306168940123</v>
       </c>
       <c r="D44">
-        <v>53.92642866294882</v>
+        <v>53.17306168940123</v>
       </c>
       <c r="E44">
-        <v>-14</v>
+        <v>-13.5</v>
       </c>
       <c r="F44">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G44">
         <v>1.85</v>
@@ -4889,45 +4889,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M44">
-        <v>1.2873</v>
+        <v>1.37815</v>
       </c>
       <c r="N44">
-        <v>3.309366666666667</v>
+        <v>3.218516666666668</v>
       </c>
       <c r="O44">
-        <v>0.7280606666666668</v>
+        <v>0.7080736666666669</v>
       </c>
       <c r="P44">
-        <v>2.581306000000001</v>
+        <v>2.510443000000001</v>
       </c>
       <c r="Q44">
-        <v>3.901306</v>
+        <v>3.830443000000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1442339104903435</v>
+        <v>0.1457180338421266</v>
       </c>
       <c r="T44">
-        <v>1.282923833831221</v>
+        <v>1.302266936333838</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.570781221678449</v>
+        <v>3.33538922952267</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1045584192900122</v>
+        <v>0.1044620104956251</v>
       </c>
       <c r="C45">
-        <v>33.52306168940123</v>
+        <v>33.11044960413567</v>
       </c>
       <c r="D45">
-        <v>53.17306168940123</v>
+        <v>53.26044960413567</v>
       </c>
       <c r="E45">
-        <v>-13.5</v>
+        <v>-13</v>
       </c>
       <c r="F45">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="G45">
         <v>1.85</v>
@@ -4971,28 +4971,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M45">
-        <v>1.37815</v>
+        <v>1.4102</v>
       </c>
       <c r="N45">
-        <v>3.218516666666668</v>
+        <v>3.186466666666667</v>
       </c>
       <c r="O45">
-        <v>0.7080736666666669</v>
+        <v>0.7010226666666668</v>
       </c>
       <c r="P45">
-        <v>2.510443000000001</v>
+        <v>2.485444000000001</v>
       </c>
       <c r="Q45">
-        <v>3.830443000000001</v>
+        <v>3.805444</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1457180338421266</v>
+        <v>0.1472551615993306</v>
       </c>
       <c r="T45">
-        <v>1.302266936333838</v>
+        <v>1.322300863925834</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.33538922952267</v>
+        <v>3.2595849288517</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1044620104956251</v>
+        <v>0.1043656017012381</v>
       </c>
       <c r="C46">
-        <v>33.11044960413567</v>
+        <v>32.69812522917307</v>
       </c>
       <c r="D46">
-        <v>53.26044960413567</v>
+        <v>53.34812522917307</v>
       </c>
       <c r="E46">
-        <v>-13</v>
+        <v>-12.5</v>
       </c>
       <c r="F46">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G46">
         <v>1.85</v>
@@ -5053,28 +5053,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M46">
-        <v>1.4102</v>
+        <v>1.44225</v>
       </c>
       <c r="N46">
-        <v>3.186466666666667</v>
+        <v>3.154416666666668</v>
       </c>
       <c r="O46">
-        <v>0.7010226666666668</v>
+        <v>0.6939716666666669</v>
       </c>
       <c r="P46">
-        <v>2.485444000000001</v>
+        <v>2.460445000000001</v>
       </c>
       <c r="Q46">
-        <v>3.805444</v>
+        <v>3.780445000000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1472551615993306</v>
+        <v>0.148848184911342</v>
       </c>
       <c r="T46">
-        <v>1.322300863925834</v>
+        <v>1.34306329797572</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.2595849288517</v>
+        <v>3.187149708210551</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1043656017012381</v>
+        <v>0.1042691929068511</v>
       </c>
       <c r="C47">
-        <v>32.69812522917307</v>
+        <v>32.28608998771433</v>
       </c>
       <c r="D47">
-        <v>53.34812522917307</v>
+        <v>53.43608998771433</v>
       </c>
       <c r="E47">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="F47">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G47">
         <v>1.85</v>
@@ -5135,28 +5135,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M47">
-        <v>1.44225</v>
+        <v>1.4743</v>
       </c>
       <c r="N47">
-        <v>3.154416666666668</v>
+        <v>3.122366666666667</v>
       </c>
       <c r="O47">
-        <v>0.6939716666666669</v>
+        <v>0.6869206666666667</v>
       </c>
       <c r="P47">
-        <v>2.460445000000001</v>
+        <v>2.435446000000001</v>
       </c>
       <c r="Q47">
-        <v>3.780445000000001</v>
+        <v>3.755446000000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.148848184911342</v>
+        <v>0.1505002090867612</v>
       </c>
       <c r="T47">
-        <v>1.34306329797572</v>
+        <v>1.36459471106449</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.187149708210551</v>
+        <v>3.117863844988582</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1042691929068511</v>
+        <v>0.104172784112464</v>
       </c>
       <c r="C48">
-        <v>32.28608998771433</v>
+        <v>31.87434531236267</v>
       </c>
       <c r="D48">
-        <v>53.43608998771433</v>
+        <v>53.52434531236267</v>
       </c>
       <c r="E48">
-        <v>-12</v>
+        <v>-11.5</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="G48">
         <v>1.85</v>
@@ -5217,28 +5217,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M48">
-        <v>1.4743</v>
+        <v>1.50635</v>
       </c>
       <c r="N48">
-        <v>3.122366666666667</v>
+        <v>3.090316666666667</v>
       </c>
       <c r="O48">
-        <v>0.6869206666666667</v>
+        <v>0.6798696666666668</v>
       </c>
       <c r="P48">
-        <v>2.435446000000001</v>
+        <v>2.410447</v>
       </c>
       <c r="Q48">
-        <v>3.755446000000001</v>
+        <v>3.730447</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1505002090867612</v>
+        <v>0.1522145737971019</v>
       </c>
       <c r="T48">
-        <v>1.36459471106449</v>
+        <v>1.386938630307555</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.117863844988582</v>
+        <v>3.051526316371804</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.104172784112464</v>
+        <v>0.106996695318077</v>
       </c>
       <c r="C49">
-        <v>31.87434531236267</v>
+        <v>28.90447340645225</v>
       </c>
       <c r="D49">
-        <v>53.52434531236267</v>
+        <v>51.05447340645225</v>
       </c>
       <c r="E49">
-        <v>-11.5</v>
+        <v>-11</v>
       </c>
       <c r="F49">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="G49">
         <v>1.85</v>
@@ -5299,45 +5299,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M49">
-        <v>1.50635</v>
+        <v>1.7256</v>
       </c>
       <c r="N49">
-        <v>3.090316666666667</v>
+        <v>2.871066666666667</v>
       </c>
       <c r="O49">
-        <v>0.6798696666666668</v>
+        <v>0.6316346666666668</v>
       </c>
       <c r="P49">
-        <v>2.410447</v>
+        <v>2.239432</v>
       </c>
       <c r="Q49">
-        <v>3.730447</v>
+        <v>3.559432</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1522145737971019</v>
+        <v>0.1539948756116865</v>
       </c>
       <c r="T49">
-        <v>1.386938630307555</v>
+        <v>1.410141931059968</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.051526316371804</v>
+        <v>2.663807757688147</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.106996695318077</v>
+        <v>0.1069611265236899</v>
       </c>
       <c r="C50">
-        <v>28.90447340645225</v>
+        <v>28.43416458727817</v>
       </c>
       <c r="D50">
-        <v>51.05447340645225</v>
+        <v>51.08416458727817</v>
       </c>
       <c r="E50">
-        <v>-11</v>
+        <v>-10.5</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G50">
         <v>1.85</v>
@@ -5381,28 +5381,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M50">
-        <v>1.7256</v>
+        <v>1.76155</v>
       </c>
       <c r="N50">
-        <v>2.871066666666668</v>
+        <v>2.835116666666667</v>
       </c>
       <c r="O50">
-        <v>0.6316346666666669</v>
+        <v>0.6237256666666668</v>
       </c>
       <c r="P50">
-        <v>2.239432000000001</v>
+        <v>2.211391000000001</v>
       </c>
       <c r="Q50">
-        <v>3.559432000000001</v>
+        <v>3.531391000000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1539948756116865</v>
+        <v>0.1558449931837058</v>
       </c>
       <c r="T50">
-        <v>1.410141931059967</v>
+        <v>1.43425516517522</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.663807757688148</v>
+        <v>2.609444334061859</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1069611265236899</v>
+        <v>0.1069255577293029</v>
       </c>
       <c r="C51">
-        <v>28.43416458727817</v>
+        <v>27.96389032253747</v>
       </c>
       <c r="D51">
-        <v>51.08416458727817</v>
+        <v>51.11389032253747</v>
       </c>
       <c r="E51">
-        <v>-10.5</v>
+        <v>-10</v>
       </c>
       <c r="F51">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G51">
         <v>1.85</v>
@@ -5463,28 +5463,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M51">
-        <v>1.76155</v>
+        <v>1.7975</v>
       </c>
       <c r="N51">
-        <v>2.835116666666667</v>
+        <v>2.799166666666667</v>
       </c>
       <c r="O51">
-        <v>0.6237256666666668</v>
+        <v>0.6158166666666668</v>
       </c>
       <c r="P51">
-        <v>2.211391000000001</v>
+        <v>2.18335</v>
       </c>
       <c r="Q51">
-        <v>3.531391000000001</v>
+        <v>3.50335</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1558449931837058</v>
+        <v>0.1577691154586058</v>
       </c>
       <c r="T51">
-        <v>1.43425516517522</v>
+        <v>1.459332928655083</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.609444334061859</v>
+        <v>2.557255447380621</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1069255577293029</v>
+        <v>0.1068899889349159</v>
       </c>
       <c r="C52">
-        <v>27.96389032253747</v>
+        <v>27.49365067258666</v>
       </c>
       <c r="D52">
-        <v>51.11389032253747</v>
+        <v>51.14365067258666</v>
       </c>
       <c r="E52">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="F52">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="G52">
         <v>1.85</v>
@@ -5545,28 +5545,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M52">
-        <v>1.7975</v>
+        <v>1.83345</v>
       </c>
       <c r="N52">
-        <v>2.799166666666667</v>
+        <v>2.763216666666668</v>
       </c>
       <c r="O52">
-        <v>0.6158166666666668</v>
+        <v>0.6079076666666668</v>
       </c>
       <c r="P52">
-        <v>2.18335</v>
+        <v>2.155309000000001</v>
       </c>
       <c r="Q52">
-        <v>3.50335</v>
+        <v>3.475309000000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1577691154586058</v>
+        <v>0.159771773336563</v>
       </c>
       <c r="T52">
-        <v>1.459332928655083</v>
+        <v>1.485434274317797</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.557255447380621</v>
+        <v>2.507113183706492</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1068899889349159</v>
+        <v>0.1084362601405288</v>
       </c>
       <c r="C53">
-        <v>27.49365067258666</v>
+        <v>25.73109198521416</v>
       </c>
       <c r="D53">
-        <v>51.14365067258666</v>
+        <v>49.88109198521416</v>
       </c>
       <c r="E53">
-        <v>-9.5</v>
+        <v>-9</v>
       </c>
       <c r="F53">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="G53">
         <v>1.85</v>
@@ -5627,45 +5627,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M53">
-        <v>1.83345</v>
+        <v>1.9708</v>
       </c>
       <c r="N53">
-        <v>2.763216666666668</v>
+        <v>2.625866666666667</v>
       </c>
       <c r="O53">
-        <v>0.6079076666666668</v>
+        <v>0.5776906666666668</v>
       </c>
       <c r="P53">
-        <v>2.155309000000001</v>
+        <v>2.048176000000001</v>
       </c>
       <c r="Q53">
-        <v>3.475309000000001</v>
+        <v>3.368176000000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.159771773336563</v>
+        <v>0.1618578752927684</v>
       </c>
       <c r="T53">
-        <v>1.485434274317797</v>
+        <v>1.512623176049791</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.507113183706492</v>
+        <v>2.332386171436304</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1084362601405288</v>
+        <v>0.1084311113461418</v>
       </c>
       <c r="C54">
-        <v>25.73109198521416</v>
+        <v>25.23519262275536</v>
       </c>
       <c r="D54">
-        <v>49.88109198521416</v>
+        <v>49.88519262275536</v>
       </c>
       <c r="E54">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="F54">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="G54">
         <v>1.85</v>
@@ -5709,28 +5709,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M54">
-        <v>1.9708</v>
+        <v>2.0087</v>
       </c>
       <c r="N54">
-        <v>2.625866666666667</v>
+        <v>2.587966666666667</v>
       </c>
       <c r="O54">
-        <v>0.5776906666666668</v>
+        <v>0.5693526666666668</v>
       </c>
       <c r="P54">
-        <v>2.048176000000001</v>
+        <v>2.018614</v>
       </c>
       <c r="Q54">
-        <v>3.368176000000001</v>
+        <v>3.338614</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1618578752927684</v>
+        <v>0.1640327475449825</v>
       </c>
       <c r="T54">
-        <v>1.512623176049791</v>
+        <v>1.540969052323572</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.332386171436304</v>
+        <v>2.288378885182788</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1084311113461418</v>
+        <v>0.1084259625517547</v>
       </c>
       <c r="C55">
-        <v>25.23519262275536</v>
+        <v>24.73929393456452</v>
       </c>
       <c r="D55">
-        <v>49.88519262275536</v>
+        <v>49.88929393456452</v>
       </c>
       <c r="E55">
-        <v>-8.5</v>
+        <v>-8</v>
       </c>
       <c r="F55">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="G55">
         <v>1.85</v>
@@ -5791,28 +5791,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M55">
-        <v>2.0087</v>
+        <v>2.0466</v>
       </c>
       <c r="N55">
-        <v>2.587966666666667</v>
+        <v>2.550066666666667</v>
       </c>
       <c r="O55">
-        <v>0.5693526666666668</v>
+        <v>0.5610146666666668</v>
       </c>
       <c r="P55">
-        <v>2.018614</v>
+        <v>1.989052</v>
       </c>
       <c r="Q55">
-        <v>3.338614</v>
+        <v>3.309052</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1640327475449825</v>
+        <v>0.1663021794603363</v>
       </c>
       <c r="T55">
-        <v>1.540969052323572</v>
+        <v>1.57054735800056</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.288378885182788</v>
+        <v>2.246001498420144</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1084259625517547</v>
+        <v>0.1084208137573677</v>
       </c>
       <c r="C56">
-        <v>24.73929393456452</v>
+        <v>24.24339592080792</v>
       </c>
       <c r="D56">
-        <v>49.88929393456452</v>
+        <v>49.89339592080792</v>
       </c>
       <c r="E56">
-        <v>-8</v>
+        <v>-7.499999999999996</v>
       </c>
       <c r="F56">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="G56">
         <v>1.85</v>
@@ -5873,28 +5873,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M56">
-        <v>2.0466</v>
+        <v>2.0845</v>
       </c>
       <c r="N56">
-        <v>2.550066666666667</v>
+        <v>2.512166666666667</v>
       </c>
       <c r="O56">
-        <v>0.5610146666666668</v>
+        <v>0.5526766666666668</v>
       </c>
       <c r="P56">
-        <v>1.989052</v>
+        <v>1.959490000000001</v>
       </c>
       <c r="Q56">
-        <v>3.309052</v>
+        <v>3.27949</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1663021794603363</v>
+        <v>0.1686724750163726</v>
       </c>
       <c r="T56">
-        <v>1.57054735800056</v>
+        <v>1.601440255040971</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.246001498420144</v>
+        <v>2.205165107539778</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1084208137573677</v>
+        <v>0.1084156649629807</v>
       </c>
       <c r="C57">
-        <v>24.24339592080792</v>
+        <v>23.74749858165195</v>
       </c>
       <c r="D57">
-        <v>49.89339592080792</v>
+        <v>49.89749858165195</v>
       </c>
       <c r="E57">
-        <v>-7.499999999999996</v>
+        <v>-6.999999999999996</v>
       </c>
       <c r="F57">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="G57">
         <v>1.85</v>
@@ -5955,28 +5955,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M57">
-        <v>2.0845</v>
+        <v>2.1224</v>
       </c>
       <c r="N57">
-        <v>2.512166666666667</v>
+        <v>2.474266666666667</v>
       </c>
       <c r="O57">
-        <v>0.5526766666666668</v>
+        <v>0.5443386666666669</v>
       </c>
       <c r="P57">
-        <v>1.959490000000001</v>
+        <v>1.929928</v>
       </c>
       <c r="Q57">
-        <v>3.27949</v>
+        <v>3.249928</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1686724750163726</v>
+        <v>0.1711505112795015</v>
       </c>
       <c r="T57">
-        <v>1.601440255040971</v>
+        <v>1.633737374674127</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.205165107539778</v>
+        <v>2.165787159190853</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1084156649629807</v>
+        <v>0.1084105161685936</v>
       </c>
       <c r="C58">
-        <v>23.74749858165195</v>
+        <v>23.25160191726307</v>
       </c>
       <c r="D58">
-        <v>49.89749858165195</v>
+        <v>49.90160191726307</v>
       </c>
       <c r="E58">
-        <v>-6.999999999999996</v>
+        <v>-6.499999999999996</v>
       </c>
       <c r="F58">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="G58">
         <v>1.85</v>
@@ -6037,28 +6037,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M58">
-        <v>2.1224</v>
+        <v>2.1603</v>
       </c>
       <c r="N58">
-        <v>2.474266666666667</v>
+        <v>2.436366666666667</v>
       </c>
       <c r="O58">
-        <v>0.5443386666666669</v>
+        <v>0.5360006666666668</v>
       </c>
       <c r="P58">
-        <v>1.929928</v>
+        <v>1.900366</v>
       </c>
       <c r="Q58">
-        <v>3.249928</v>
+        <v>3.220366</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1711505112795015</v>
+        <v>0.173743805043241</v>
       </c>
       <c r="T58">
-        <v>1.633737374674127</v>
+        <v>1.667536685918128</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.165787159190853</v>
+        <v>2.127790893240137</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1084105161685936</v>
+        <v>0.1084053673742066</v>
       </c>
       <c r="C59">
-        <v>23.25160191726307</v>
+        <v>22.75570592780774</v>
       </c>
       <c r="D59">
-        <v>49.90160191726307</v>
+        <v>49.90570592780774</v>
       </c>
       <c r="E59">
-        <v>-6.499999999999996</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="F59">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="G59">
         <v>1.85</v>
@@ -6119,28 +6119,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M59">
-        <v>2.1603</v>
+        <v>2.1982</v>
       </c>
       <c r="N59">
-        <v>2.436366666666667</v>
+        <v>2.398466666666667</v>
       </c>
       <c r="O59">
-        <v>0.5360006666666668</v>
+        <v>0.5276626666666668</v>
       </c>
       <c r="P59">
-        <v>1.900366</v>
+        <v>1.870804</v>
       </c>
       <c r="Q59">
-        <v>3.220366</v>
+        <v>3.190804</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.173743805043241</v>
+        <v>0.1764605889862061</v>
       </c>
       <c r="T59">
-        <v>1.667536685918128</v>
+        <v>1.702945488173748</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.127790893240137</v>
+        <v>2.091104843356686</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1084053673742066</v>
+        <v>0.1084002185798195</v>
       </c>
       <c r="C60">
-        <v>22.75570592780773</v>
+        <v>22.25981061345248</v>
       </c>
       <c r="D60">
-        <v>49.90570592780772</v>
+        <v>49.90981061345248</v>
       </c>
       <c r="E60">
-        <v>-6.000000000000004</v>
+        <v>-5.5</v>
       </c>
       <c r="F60">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="G60">
         <v>1.85</v>
@@ -6201,28 +6201,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M60">
-        <v>2.1982</v>
+        <v>2.2361</v>
       </c>
       <c r="N60">
-        <v>2.398466666666668</v>
+        <v>2.360566666666668</v>
       </c>
       <c r="O60">
-        <v>0.5276626666666668</v>
+        <v>0.5193246666666669</v>
       </c>
       <c r="P60">
-        <v>1.870804000000001</v>
+        <v>1.841242000000001</v>
       </c>
       <c r="Q60">
-        <v>3.190804000000001</v>
+        <v>3.161242000000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1764605889862061</v>
+        <v>0.1793098989751696</v>
       </c>
       <c r="T60">
-        <v>1.702945488173748</v>
+        <v>1.740081549075984</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.091104843356686</v>
+        <v>2.055662388384539</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1084002185798195</v>
+        <v>0.1083950697854325</v>
       </c>
       <c r="C61">
-        <v>22.25981061345248</v>
+        <v>21.7639159743639</v>
       </c>
       <c r="D61">
-        <v>49.90981061345248</v>
+        <v>49.9139159743639</v>
       </c>
       <c r="E61">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="F61">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="G61">
         <v>1.85</v>
@@ -6283,28 +6283,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M61">
-        <v>2.2361</v>
+        <v>2.274</v>
       </c>
       <c r="N61">
-        <v>2.360566666666668</v>
+        <v>2.322666666666668</v>
       </c>
       <c r="O61">
-        <v>0.5193246666666669</v>
+        <v>0.5109866666666668</v>
       </c>
       <c r="P61">
-        <v>1.841242000000001</v>
+        <v>1.811680000000001</v>
       </c>
       <c r="Q61">
-        <v>3.161242000000001</v>
+        <v>3.131680000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1793098989751696</v>
+        <v>0.1823016744635812</v>
       </c>
       <c r="T61">
-        <v>1.740081549075984</v>
+        <v>1.779074413023331</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.055662388384539</v>
+        <v>2.02140134857813</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1083950697854325</v>
+        <v>0.1151462809910454</v>
       </c>
       <c r="C62">
-        <v>21.7639159743639</v>
+        <v>16.40454379136735</v>
       </c>
       <c r="D62">
-        <v>49.9139159743639</v>
+        <v>45.05454379136735</v>
       </c>
       <c r="E62">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
       <c r="F62">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="G62">
         <v>1.85</v>
@@ -6365,45 +6365,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M62">
-        <v>2.274</v>
+        <v>2.745</v>
       </c>
       <c r="N62">
-        <v>2.322666666666668</v>
+        <v>1.851666666666667</v>
       </c>
       <c r="O62">
-        <v>0.5109866666666668</v>
+        <v>0.4073666666666668</v>
       </c>
       <c r="P62">
-        <v>1.811680000000001</v>
+        <v>1.444300000000001</v>
       </c>
       <c r="Q62">
-        <v>3.131680000000001</v>
+        <v>2.7643</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1823016744635812</v>
+        <v>0.1854468743360139</v>
       </c>
       <c r="T62">
-        <v>1.779074413023331</v>
+        <v>1.82006691101926</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.02140134857813</v>
+        <v>1.674559805707347</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1151462809910454</v>
+        <v>0.1152518921966584</v>
       </c>
       <c r="C63">
-        <v>16.40454379136735</v>
+        <v>15.83603212757172</v>
       </c>
       <c r="D63">
-        <v>45.05454379136735</v>
+        <v>44.98603212757172</v>
       </c>
       <c r="E63">
-        <v>-4.5</v>
+        <v>-4</v>
       </c>
       <c r="F63">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G63">
         <v>1.85</v>
@@ -6447,28 +6447,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M63">
-        <v>2.745</v>
+        <v>2.79</v>
       </c>
       <c r="N63">
-        <v>1.851666666666667</v>
+        <v>1.806666666666668</v>
       </c>
       <c r="O63">
-        <v>0.4073666666666668</v>
+        <v>0.3974666666666669</v>
       </c>
       <c r="P63">
-        <v>1.444300000000001</v>
+        <v>1.409200000000001</v>
       </c>
       <c r="Q63">
-        <v>2.7643</v>
+        <v>2.729200000000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1854468743360139</v>
+        <v>0.1887576110438379</v>
       </c>
       <c r="T63">
-        <v>1.82006691101926</v>
+        <v>1.863216908909712</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.674559805707347</v>
+        <v>1.647550776583035</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1152518921966584</v>
+        <v>0.1153575034022714</v>
       </c>
       <c r="C64">
-        <v>15.83603212757172</v>
+        <v>15.26772851032916</v>
       </c>
       <c r="D64">
-        <v>44.98603212757172</v>
+        <v>44.91772851032916</v>
       </c>
       <c r="E64">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="F64">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G64">
         <v>1.85</v>
@@ -6529,28 +6529,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M64">
-        <v>2.79</v>
+        <v>2.835</v>
       </c>
       <c r="N64">
-        <v>1.806666666666668</v>
+        <v>1.761666666666668</v>
       </c>
       <c r="O64">
-        <v>0.3974666666666669</v>
+        <v>0.3875666666666669</v>
       </c>
       <c r="P64">
-        <v>1.409200000000001</v>
+        <v>1.374100000000001</v>
       </c>
       <c r="Q64">
-        <v>2.729200000000001</v>
+        <v>2.694100000000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1887576110438379</v>
+        <v>0.1922473064926253</v>
       </c>
       <c r="T64">
-        <v>1.863216908909712</v>
+        <v>1.908699339118567</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.647550776583035</v>
+        <v>1.621399176954733</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1153575034022714</v>
+        <v>0.1154631146078843</v>
       </c>
       <c r="C65">
-        <v>15.26772851032916</v>
+        <v>14.69963199342672</v>
       </c>
       <c r="D65">
-        <v>44.91772851032916</v>
+        <v>44.84963199342672</v>
       </c>
       <c r="E65">
-        <v>-3.5</v>
+        <v>-3</v>
       </c>
       <c r="F65">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="G65">
         <v>1.85</v>
@@ -6611,28 +6611,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M65">
-        <v>2.835</v>
+        <v>2.88</v>
       </c>
       <c r="N65">
-        <v>1.761666666666668</v>
+        <v>1.716666666666668</v>
       </c>
       <c r="O65">
-        <v>0.3875666666666669</v>
+        <v>0.3776666666666669</v>
       </c>
       <c r="P65">
-        <v>1.374100000000001</v>
+        <v>1.339000000000001</v>
       </c>
       <c r="Q65">
-        <v>2.694100000000001</v>
+        <v>2.659000000000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1922473064926253</v>
+        <v>0.1959308739107898</v>
       </c>
       <c r="T65">
-        <v>1.908699339118567</v>
+        <v>1.956708571005692</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.621399176954733</v>
+        <v>1.596064814814815</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1154631146078843</v>
+        <v>0.1155687258134973</v>
       </c>
       <c r="C66">
-        <v>14.69963199342672</v>
+        <v>14.13174163638072</v>
       </c>
       <c r="D66">
-        <v>44.84963199342672</v>
+        <v>44.78174163638072</v>
       </c>
       <c r="E66">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="F66">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G66">
         <v>1.85</v>
@@ -6693,28 +6693,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M66">
-        <v>2.88</v>
+        <v>2.925</v>
       </c>
       <c r="N66">
-        <v>1.716666666666668</v>
+        <v>1.671666666666668</v>
       </c>
       <c r="O66">
-        <v>0.3776666666666669</v>
+        <v>0.3677666666666669</v>
       </c>
       <c r="P66">
-        <v>1.339000000000001</v>
+        <v>1.303900000000001</v>
       </c>
       <c r="Q66">
-        <v>2.659000000000001</v>
+        <v>2.623900000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1959308739107898</v>
+        <v>0.1998249308957065</v>
       </c>
       <c r="T66">
-        <v>1.956708571005692</v>
+        <v>2.00746118757208</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.596064814814815</v>
+        <v>1.571509971509972</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1155687258134973</v>
+        <v>0.1156743370191102</v>
       </c>
       <c r="C67">
-        <v>14.13174163638072</v>
+        <v>13.56405650439339</v>
       </c>
       <c r="D67">
-        <v>44.78174163638072</v>
+        <v>44.71405650439339</v>
       </c>
       <c r="E67">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="F67">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="G67">
         <v>1.85</v>
@@ -6775,28 +6775,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M67">
-        <v>2.925</v>
+        <v>2.97</v>
       </c>
       <c r="N67">
-        <v>1.671666666666668</v>
+        <v>1.626666666666668</v>
       </c>
       <c r="O67">
-        <v>0.3677666666666669</v>
+        <v>0.3578666666666669</v>
       </c>
       <c r="P67">
-        <v>1.303900000000001</v>
+        <v>1.268800000000001</v>
       </c>
       <c r="Q67">
-        <v>2.623900000000001</v>
+        <v>2.588800000000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1998249308957065</v>
+        <v>0.2039480500562066</v>
       </c>
       <c r="T67">
-        <v>2.00746118757208</v>
+        <v>2.061199252171786</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.571509971509972</v>
+        <v>1.547699214365881</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1156743370191102</v>
+        <v>0.1157799482247232</v>
       </c>
       <c r="C68">
-        <v>13.56405650439339</v>
+        <v>12.99657566831003</v>
       </c>
       <c r="D68">
-        <v>44.71405650439339</v>
+        <v>44.64657566831003</v>
       </c>
       <c r="E68">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="F68">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G68">
         <v>1.85</v>
@@ -6857,28 +6857,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M68">
-        <v>2.97</v>
+        <v>3.015</v>
       </c>
       <c r="N68">
-        <v>1.626666666666668</v>
+        <v>1.581666666666668</v>
       </c>
       <c r="O68">
-        <v>0.3578666666666669</v>
+        <v>0.3479666666666669</v>
       </c>
       <c r="P68">
-        <v>1.268800000000001</v>
+        <v>1.233700000000001</v>
       </c>
       <c r="Q68">
-        <v>2.588800000000001</v>
+        <v>2.553700000000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2039480500562066</v>
+        <v>0.2083210552264339</v>
       </c>
       <c r="T68">
-        <v>2.061199252171786</v>
+        <v>2.118194169171474</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.547699214365881</v>
+        <v>1.524599226091764</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1157799482247232</v>
+        <v>0.1158855594303362</v>
       </c>
       <c r="C69">
-        <v>12.99657566831003</v>
+        <v>12.42929820457646</v>
       </c>
       <c r="D69">
-        <v>44.64657566831003</v>
+        <v>44.57929820457646</v>
       </c>
       <c r="E69">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="F69">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="G69">
         <v>1.85</v>
@@ -6939,28 +6939,28 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M69">
-        <v>3.015</v>
+        <v>3.06</v>
       </c>
       <c r="N69">
-        <v>1.581666666666668</v>
+        <v>1.536666666666668</v>
       </c>
       <c r="O69">
-        <v>0.3479666666666669</v>
+        <v>0.3380666666666668</v>
       </c>
       <c r="P69">
-        <v>1.233700000000001</v>
+        <v>1.198600000000001</v>
       </c>
       <c r="Q69">
-        <v>2.553700000000001</v>
+        <v>2.518600000000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2083210552264339</v>
+        <v>0.2129673732198005</v>
       </c>
       <c r="T69">
-        <v>2.118194169171474</v>
+        <v>2.178751268483642</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.524599226091764</v>
+        <v>1.502178649237473</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1158855594303362</v>
+        <v>0.1495020815785492</v>
       </c>
       <c r="C70">
-        <v>12.42929820457646</v>
+        <v>-2.521722861098308</v>
       </c>
       <c r="D70">
-        <v>44.57929820457646</v>
+        <v>30.12827713890169</v>
       </c>
       <c r="E70">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="F70">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="G70">
         <v>1.85</v>
@@ -7021,45 +7021,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M70">
-        <v>3.06</v>
+        <v>5.0646</v>
       </c>
       <c r="N70">
-        <v>1.536666666666668</v>
+        <v>-0.4679333333333329</v>
       </c>
       <c r="O70">
-        <v>0.3380666666666668</v>
+        <v>-0.1029453333333332</v>
       </c>
       <c r="P70">
-        <v>1.198600000000001</v>
+        <v>-0.3649879999999996</v>
       </c>
       <c r="Q70">
-        <v>2.518600000000001</v>
+        <v>0.9550120000000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2129673732198005</v>
+        <v>0.2207594029415564</v>
       </c>
       <c r="T70">
-        <v>2.178751268483642</v>
+        <v>2.28030753699075</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.22</v>
+        <v>0.1996735510537193</v>
       </c>
       <c r="W70">
-        <v>0.0702</v>
+        <v>0.117487922705314</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.502178649237473</v>
+        <v>0.9076070502441786</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1495020815785492</v>
+        <v>0.1505120815785492</v>
       </c>
       <c r="C71">
-        <v>-2.521722861098308</v>
+        <v>-3.312325048081519</v>
       </c>
       <c r="D71">
-        <v>30.12827713890169</v>
+        <v>29.83767495191848</v>
       </c>
       <c r="E71">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="G71">
         <v>1.85</v>
@@ -7103,37 +7103,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M71">
-        <v>5.0646</v>
+        <v>5.138000000000001</v>
       </c>
       <c r="N71">
-        <v>-0.4679333333333329</v>
+        <v>-0.5413333333333332</v>
       </c>
       <c r="O71">
-        <v>-0.1029453333333332</v>
+        <v>-0.1190933333333333</v>
       </c>
       <c r="P71">
-        <v>-0.3649879999999996</v>
+        <v>-0.4222399999999999</v>
       </c>
       <c r="Q71">
-        <v>0.9550120000000002</v>
+        <v>0.8977599999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2207594029415564</v>
+        <v>0.2265913830396083</v>
       </c>
       <c r="T71">
-        <v>2.28030753699075</v>
+        <v>2.356317788223775</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1996735510537193</v>
+        <v>0.1968210717529519</v>
       </c>
       <c r="W71">
-        <v>0.117487922705314</v>
+        <v>0.1179066666666667</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9076070502441786</v>
+        <v>0.8946412352406903</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1505120815785492</v>
+        <v>0.1515220815785492</v>
       </c>
       <c r="C72">
-        <v>-3.312325048081519</v>
+        <v>-4.097374786522849</v>
       </c>
       <c r="D72">
-        <v>29.83767495191848</v>
+        <v>29.55262521347716</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>0.5000000000000071</v>
       </c>
       <c r="F72">
-        <v>35</v>
+        <v>35.50000000000001</v>
       </c>
       <c r="G72">
         <v>1.85</v>
@@ -7185,37 +7185,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M72">
-        <v>5.138000000000001</v>
+        <v>5.211400000000001</v>
       </c>
       <c r="N72">
-        <v>-0.5413333333333332</v>
+        <v>-0.6147333333333336</v>
       </c>
       <c r="O72">
-        <v>-0.1190933333333333</v>
+        <v>-0.1352413333333334</v>
       </c>
       <c r="P72">
-        <v>-0.4222399999999999</v>
+        <v>-0.4794920000000002</v>
       </c>
       <c r="Q72">
-        <v>0.8977599999999999</v>
+        <v>0.8405079999999996</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2265913830396083</v>
+        <v>0.2328255686616638</v>
       </c>
       <c r="T72">
-        <v>2.356317788223775</v>
+        <v>2.437570125748733</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1968210717529519</v>
+        <v>0.1940489439817835</v>
       </c>
       <c r="W72">
-        <v>0.1179066666666667</v>
+        <v>0.1183136150234742</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8946412352406903</v>
+        <v>0.8820406544626523</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1515220815785491</v>
+        <v>0.1525320815785491</v>
       </c>
       <c r="C73">
-        <v>-4.097374786522831</v>
+        <v>-4.877029703996214</v>
       </c>
       <c r="D73">
-        <v>29.55262521347717</v>
+        <v>29.27297029600378</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="G73">
         <v>1.85</v>
@@ -7267,37 +7267,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M73">
-        <v>5.2114</v>
+        <v>5.284800000000001</v>
       </c>
       <c r="N73">
-        <v>-0.6147333333333327</v>
+        <v>-0.688133333333333</v>
       </c>
       <c r="O73">
-        <v>-0.1352413333333332</v>
+        <v>-0.1513893333333333</v>
       </c>
       <c r="P73">
-        <v>-0.4794919999999995</v>
+        <v>-0.5367439999999998</v>
       </c>
       <c r="Q73">
-        <v>0.8405080000000004</v>
+        <v>0.7832560000000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2328255686616637</v>
+        <v>0.2395050532567231</v>
       </c>
       <c r="T73">
-        <v>2.437570125748731</v>
+        <v>2.524626201668329</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1940489439817836</v>
+        <v>0.1913538197598143</v>
       </c>
       <c r="W73">
-        <v>0.1183136150234742</v>
+        <v>0.1187092592592593</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8820406544626526</v>
+        <v>0.8697900898173379</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1525320815785491</v>
+        <v>0.1535420815785491</v>
       </c>
       <c r="C74">
-        <v>-4.877029703996214</v>
+        <v>-5.651441517521548</v>
       </c>
       <c r="D74">
-        <v>29.27297029600378</v>
+        <v>28.99855848247845</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F74">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G74">
         <v>1.85</v>
@@ -7349,37 +7349,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M74">
-        <v>5.284800000000001</v>
+        <v>5.3582</v>
       </c>
       <c r="N74">
-        <v>-0.688133333333333</v>
+        <v>-0.7615333333333325</v>
       </c>
       <c r="O74">
-        <v>-0.1513893333333333</v>
+        <v>-0.1675373333333331</v>
       </c>
       <c r="P74">
-        <v>-0.5367439999999998</v>
+        <v>-0.5939959999999993</v>
       </c>
       <c r="Q74">
-        <v>0.7832560000000001</v>
+        <v>0.7260040000000005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2395050532567231</v>
+        <v>0.2466793144884536</v>
       </c>
       <c r="T74">
-        <v>2.524626201668329</v>
+        <v>2.618130875804193</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1913538197598143</v>
+        <v>0.1887325345576251</v>
       </c>
       <c r="W74">
-        <v>0.1187092592592593</v>
+        <v>0.1190940639269406</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8697900898173379</v>
+        <v>0.8578751570801142</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1535420815785491</v>
+        <v>0.1545520815785492</v>
       </c>
       <c r="C75">
-        <v>-5.651441517521548</v>
+        <v>-6.420756308026494</v>
       </c>
       <c r="D75">
-        <v>28.99855848247845</v>
+        <v>28.7292436919735</v>
       </c>
       <c r="E75">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="G75">
         <v>1.85</v>
@@ -7431,37 +7431,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M75">
-        <v>5.3582</v>
+        <v>5.4316</v>
       </c>
       <c r="N75">
-        <v>-0.7615333333333325</v>
+        <v>-0.8349333333333329</v>
       </c>
       <c r="O75">
-        <v>-0.1675373333333331</v>
+        <v>-0.1836853333333332</v>
       </c>
       <c r="P75">
-        <v>-0.5939959999999993</v>
+        <v>-0.6512479999999996</v>
       </c>
       <c r="Q75">
-        <v>0.7260040000000005</v>
+        <v>0.6687520000000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2466793144884536</v>
+        <v>0.2544054419687788</v>
       </c>
       <c r="T75">
-        <v>2.618130875804193</v>
+        <v>2.718828217181278</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1887325345576251</v>
+        <v>0.186182094901441</v>
       </c>
       <c r="W75">
-        <v>0.1190940639269406</v>
+        <v>0.1194684684684685</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8578751570801142</v>
+        <v>0.8462822495520044</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1545520815785492</v>
+        <v>0.1555620815785492</v>
       </c>
       <c r="C76">
-        <v>-6.420756308026494</v>
+        <v>-7.185114779655226</v>
       </c>
       <c r="D76">
-        <v>28.7292436919735</v>
+        <v>28.46488522034477</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F76">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G76">
         <v>1.85</v>
@@ -7513,37 +7513,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M76">
-        <v>5.4316</v>
+        <v>5.505000000000001</v>
       </c>
       <c r="N76">
-        <v>-0.8349333333333329</v>
+        <v>-0.9083333333333332</v>
       </c>
       <c r="O76">
-        <v>-0.1836853333333332</v>
+        <v>-0.1998333333333333</v>
       </c>
       <c r="P76">
-        <v>-0.6512479999999996</v>
+        <v>-0.7084999999999999</v>
       </c>
       <c r="Q76">
-        <v>0.6687520000000002</v>
+        <v>0.6114999999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2544054419687788</v>
+        <v>0.2627496596475299</v>
       </c>
       <c r="T76">
-        <v>2.718828217181278</v>
+        <v>2.827581345868529</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.186182094901441</v>
+        <v>0.1836996669694217</v>
       </c>
       <c r="W76">
-        <v>0.1194684684684685</v>
+        <v>0.1198328888888889</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8462822495520044</v>
+        <v>0.8349984862246443</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1555620815785492</v>
+        <v>0.1565720815785492</v>
       </c>
       <c r="C77">
-        <v>-7.185114779655226</v>
+        <v>-7.944652504891188</v>
       </c>
       <c r="D77">
-        <v>28.46488522034477</v>
+        <v>28.20534749510881</v>
       </c>
       <c r="E77">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="G77">
         <v>1.85</v>
@@ -7595,37 +7595,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M77">
-        <v>5.505000000000001</v>
+        <v>5.5784</v>
       </c>
       <c r="N77">
-        <v>-0.9083333333333332</v>
+        <v>-0.9817333333333327</v>
       </c>
       <c r="O77">
-        <v>-0.1998333333333333</v>
+        <v>-0.2159813333333332</v>
       </c>
       <c r="P77">
-        <v>-0.7084999999999999</v>
+        <v>-0.7657519999999995</v>
       </c>
       <c r="Q77">
-        <v>0.6114999999999999</v>
+        <v>0.5542480000000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2627496596475299</v>
+        <v>0.2717892287995103</v>
       </c>
       <c r="T77">
-        <v>2.827581345868529</v>
+        <v>2.945397235279718</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1836996669694217</v>
+        <v>0.1812825660882452</v>
       </c>
       <c r="W77">
-        <v>0.1198328888888889</v>
+        <v>0.1201877192982456</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8349984862246443</v>
+        <v>0.8240116640374781</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1565720815785492</v>
+        <v>0.1575820815785491</v>
       </c>
       <c r="C78">
-        <v>-7.944652504891188</v>
+        <v>-8.699500156391039</v>
       </c>
       <c r="D78">
-        <v>28.20534749510881</v>
+        <v>27.95049984360896</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F78">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G78">
         <v>1.85</v>
@@ -7677,37 +7677,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M78">
-        <v>5.5784</v>
+        <v>5.651800000000001</v>
       </c>
       <c r="N78">
-        <v>-0.9817333333333327</v>
+        <v>-1.055133333333333</v>
       </c>
       <c r="O78">
-        <v>-0.2159813333333332</v>
+        <v>-0.2321293333333333</v>
       </c>
       <c r="P78">
-        <v>-0.7657519999999995</v>
+        <v>-0.8230039999999997</v>
       </c>
       <c r="Q78">
-        <v>0.5542480000000003</v>
+        <v>0.4969960000000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2717892287995103</v>
+        <v>0.2816148474429673</v>
       </c>
       <c r="T78">
-        <v>2.945397235279718</v>
+        <v>3.073457984639705</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1812825660882452</v>
+        <v>0.1789282470481381</v>
       </c>
       <c r="W78">
-        <v>0.1201877192982456</v>
+        <v>0.1205333333333333</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8240116640374781</v>
+        <v>0.8133102138551731</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1575820815785491</v>
+        <v>0.1585920815785491</v>
       </c>
       <c r="C79">
-        <v>-8.699500156391039</v>
+        <v>-9.44978372636298</v>
       </c>
       <c r="D79">
-        <v>27.95049984360896</v>
+        <v>27.70021627363702</v>
       </c>
       <c r="E79">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="G79">
         <v>1.85</v>
@@ -7759,37 +7759,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M79">
-        <v>5.651800000000001</v>
+        <v>5.725200000000001</v>
       </c>
       <c r="N79">
-        <v>-1.055133333333333</v>
+        <v>-1.128533333333333</v>
       </c>
       <c r="O79">
-        <v>-0.2321293333333333</v>
+        <v>-0.2482773333333333</v>
       </c>
       <c r="P79">
-        <v>-0.8230039999999997</v>
+        <v>-0.880256</v>
       </c>
       <c r="Q79">
-        <v>0.4969960000000001</v>
+        <v>0.4397439999999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2816148474429673</v>
+        <v>0.2923337041449204</v>
       </c>
       <c r="T79">
-        <v>3.073457984639705</v>
+        <v>3.213160620305147</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1789282470481381</v>
+        <v>0.1766342951629055</v>
       </c>
       <c r="W79">
-        <v>0.1205333333333333</v>
+        <v>0.1208700854700855</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8133102138551731</v>
+        <v>0.8028831598313888</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1585920815785491</v>
+        <v>0.2045927362448127</v>
       </c>
       <c r="C80">
-        <v>-9.44978372636298</v>
+        <v>-17.97425709408615</v>
       </c>
       <c r="D80">
-        <v>27.70021627363702</v>
+        <v>19.67574290591385</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F80">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="G80">
         <v>1.85</v>
@@ -7841,45 +7841,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M80">
-        <v>5.725200000000001</v>
+        <v>7.9316</v>
       </c>
       <c r="N80">
-        <v>-1.128533333333333</v>
+        <v>-3.334933333333333</v>
       </c>
       <c r="O80">
-        <v>-0.2482773333333333</v>
+        <v>-0.7336853333333332</v>
       </c>
       <c r="P80">
-        <v>-0.880256</v>
+        <v>-2.601248</v>
       </c>
       <c r="Q80">
-        <v>0.4397439999999998</v>
+        <v>-1.281248</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2923337041449204</v>
+        <v>0.3151717598959333</v>
       </c>
       <c r="T80">
-        <v>3.213160620305147</v>
+        <v>3.510817046788528</v>
       </c>
       <c r="U80">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1766342951629055</v>
+        <v>0.1274984450384118</v>
       </c>
       <c r="W80">
-        <v>0.1208700854700855</v>
+        <v>0.1751983122362869</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8028831598313888</v>
+        <v>0.5795383865382353</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2045927362448127</v>
+        <v>0.2061427362448127</v>
       </c>
       <c r="C81">
-        <v>-17.97425709408615</v>
+        <v>-18.66445842292966</v>
       </c>
       <c r="D81">
-        <v>19.67574290591385</v>
+        <v>19.48554157707034</v>
       </c>
       <c r="E81">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F81">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="G81">
         <v>1.85</v>
@@ -7923,37 +7923,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M81">
-        <v>7.9316</v>
+        <v>8.032</v>
       </c>
       <c r="N81">
-        <v>-3.334933333333333</v>
+        <v>-3.435333333333332</v>
       </c>
       <c r="O81">
-        <v>-0.7336853333333332</v>
+        <v>-0.7557733333333332</v>
       </c>
       <c r="P81">
-        <v>-2.601248</v>
+        <v>-2.679559999999999</v>
       </c>
       <c r="Q81">
-        <v>-1.281248</v>
+        <v>-1.35956</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3151717598959333</v>
+        <v>0.32864034789073</v>
       </c>
       <c r="T81">
-        <v>3.510817046788528</v>
+        <v>3.686357899127955</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1274984450384118</v>
+        <v>0.1259047144754316</v>
       </c>
       <c r="W81">
-        <v>0.1751983122362869</v>
+        <v>0.1755183333333333</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5795383865382353</v>
+        <v>0.5722941567065074</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2061427362448127</v>
+        <v>0.2076927362448127</v>
       </c>
       <c r="C82">
-        <v>-18.66445842292966</v>
+        <v>-19.35101768522285</v>
       </c>
       <c r="D82">
-        <v>19.48554157707034</v>
+        <v>19.29898231477715</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F82">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G82">
         <v>1.85</v>
@@ -8005,37 +8005,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M82">
-        <v>8.032</v>
+        <v>8.132400000000001</v>
       </c>
       <c r="N82">
-        <v>-3.435333333333332</v>
+        <v>-3.535733333333333</v>
       </c>
       <c r="O82">
-        <v>-0.7557733333333332</v>
+        <v>-0.7778613333333333</v>
       </c>
       <c r="P82">
-        <v>-2.679559999999999</v>
+        <v>-2.757872</v>
       </c>
       <c r="Q82">
-        <v>-1.35956</v>
+        <v>-1.437872</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.32864034789073</v>
+        <v>0.3435266819902421</v>
       </c>
       <c r="T82">
-        <v>3.686357899127955</v>
+        <v>3.880376735924163</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1259047144754316</v>
+        <v>0.1243503352843769</v>
       </c>
       <c r="W82">
-        <v>0.1755183333333333</v>
+        <v>0.1758304526748971</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5722941567065074</v>
+        <v>0.5652287967471679</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2076927362448127</v>
+        <v>0.2092427362448127</v>
       </c>
       <c r="C83">
-        <v>-19.35101768522285</v>
+        <v>-20.03403849896583</v>
       </c>
       <c r="D83">
-        <v>19.29898231477715</v>
+        <v>19.11596150103417</v>
       </c>
       <c r="E83">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="F83">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="G83">
         <v>1.85</v>
@@ -8087,37 +8087,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M83">
-        <v>8.132400000000001</v>
+        <v>8.232800000000001</v>
       </c>
       <c r="N83">
-        <v>-3.535733333333333</v>
+        <v>-3.636133333333333</v>
       </c>
       <c r="O83">
-        <v>-0.7778613333333333</v>
+        <v>-0.7999493333333334</v>
       </c>
       <c r="P83">
-        <v>-2.757872</v>
+        <v>-2.836184</v>
       </c>
       <c r="Q83">
-        <v>-1.437872</v>
+        <v>-1.516184</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3435266819902421</v>
+        <v>0.3600670532119223</v>
       </c>
       <c r="T83">
-        <v>3.880376735924163</v>
+        <v>4.095953221253285</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1243503352843769</v>
+        <v>0.1228338677809089</v>
       </c>
       <c r="W83">
-        <v>0.1758304526748971</v>
+        <v>0.1761349593495935</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5652287967471679</v>
+        <v>0.558335762640495</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2092427362448127</v>
+        <v>0.2107927362448127</v>
       </c>
       <c r="C84">
-        <v>-20.03403849896583</v>
+        <v>-20.71362058846242</v>
       </c>
       <c r="D84">
-        <v>19.11596150103417</v>
+        <v>18.93637941153758</v>
       </c>
       <c r="E84">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F84">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="G84">
         <v>1.85</v>
@@ -8169,37 +8169,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M84">
-        <v>8.232800000000001</v>
+        <v>8.3332</v>
       </c>
       <c r="N84">
-        <v>-3.636133333333333</v>
+        <v>-3.736533333333332</v>
       </c>
       <c r="O84">
-        <v>-0.7999493333333334</v>
+        <v>-0.8220373333333331</v>
       </c>
       <c r="P84">
-        <v>-2.836184</v>
+        <v>-2.914495999999999</v>
       </c>
       <c r="Q84">
-        <v>-1.516184</v>
+        <v>-1.594495999999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3600670532119223</v>
+        <v>0.3785533504596824</v>
       </c>
       <c r="T84">
-        <v>4.095953221253285</v>
+        <v>4.336891646032889</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1228338677809089</v>
+        <v>0.1213539416630666</v>
       </c>
       <c r="W84">
-        <v>0.1761349593495935</v>
+        <v>0.1764321285140562</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.558335762640495</v>
+        <v>0.5516088257412119</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2107927362448127</v>
+        <v>0.2123427362448126</v>
       </c>
       <c r="C85">
-        <v>-20.71362058846242</v>
+        <v>-21.38985996551179</v>
       </c>
       <c r="D85">
-        <v>18.93637941153758</v>
+        <v>18.76014003448821</v>
       </c>
       <c r="E85">
-        <v>6.5</v>
+        <v>7.000000000000007</v>
       </c>
       <c r="F85">
-        <v>41.5</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="G85">
         <v>1.85</v>
@@ -8251,37 +8251,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M85">
-        <v>8.3332</v>
+        <v>8.433600000000002</v>
       </c>
       <c r="N85">
-        <v>-3.736533333333332</v>
+        <v>-3.836933333333334</v>
       </c>
       <c r="O85">
-        <v>-0.8220373333333331</v>
+        <v>-0.8441253333333336</v>
       </c>
       <c r="P85">
-        <v>-2.914495999999999</v>
+        <v>-2.992808000000001</v>
       </c>
       <c r="Q85">
-        <v>-1.594495999999999</v>
+        <v>-1.672808000000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3785533504596824</v>
+        <v>0.3993504348634126</v>
       </c>
       <c r="T85">
-        <v>4.336891646032889</v>
+        <v>4.607947373909945</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1213539416630666</v>
+        <v>0.1199092518813634</v>
       </c>
       <c r="W85">
-        <v>0.1764321285140562</v>
+        <v>0.1767222222222222</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5516088257412119</v>
+        <v>0.5450420540061974</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2123427362448126</v>
+        <v>0.2138927362448126</v>
       </c>
       <c r="C86">
-        <v>-21.38985996551179</v>
+        <v>-22.06284910057534</v>
       </c>
       <c r="D86">
-        <v>18.76014003448821</v>
+        <v>18.58715089942466</v>
       </c>
       <c r="E86">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F86">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G86">
         <v>1.85</v>
@@ -8333,37 +8333,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M86">
-        <v>8.4336</v>
+        <v>8.534000000000001</v>
       </c>
       <c r="N86">
-        <v>-3.836933333333333</v>
+        <v>-3.937333333333333</v>
       </c>
       <c r="O86">
-        <v>-0.8441253333333332</v>
+        <v>-0.8662133333333333</v>
       </c>
       <c r="P86">
-        <v>-2.992807999999999</v>
+        <v>-3.07112</v>
       </c>
       <c r="Q86">
-        <v>-1.672807999999999</v>
+        <v>-1.75112</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3993504348634124</v>
+        <v>0.4229204638543065</v>
       </c>
       <c r="T86">
-        <v>4.607947373909942</v>
+        <v>4.915143865503938</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1199092518813635</v>
+        <v>0.1184985548004062</v>
       </c>
       <c r="W86">
-        <v>0.1767222222222222</v>
+        <v>0.1770054901960784</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5450420540061975</v>
+        <v>0.5386297945473011</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2138927362448126</v>
+        <v>0.2154427362448126</v>
       </c>
       <c r="C87">
-        <v>-22.06284910057534</v>
+        <v>-22.73267708456006</v>
       </c>
       <c r="D87">
-        <v>18.58715089942466</v>
+        <v>18.41732291543994</v>
       </c>
       <c r="E87">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F87">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="G87">
         <v>1.85</v>
@@ -8415,37 +8415,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M87">
-        <v>8.534000000000001</v>
+        <v>8.634399999999999</v>
       </c>
       <c r="N87">
-        <v>-3.937333333333333</v>
+        <v>-4.037733333333332</v>
       </c>
       <c r="O87">
-        <v>-0.8662133333333333</v>
+        <v>-0.8883013333333331</v>
       </c>
       <c r="P87">
-        <v>-3.07112</v>
+        <v>-3.149431999999999</v>
       </c>
       <c r="Q87">
-        <v>-1.75112</v>
+        <v>-1.829431999999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4229204638543065</v>
+        <v>0.4498576398438999</v>
       </c>
       <c r="T87">
-        <v>4.915143865503938</v>
+        <v>5.266225570182792</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1184985548004062</v>
+        <v>0.1171206646283085</v>
       </c>
       <c r="W87">
-        <v>0.1770054901960784</v>
+        <v>0.1772821705426356</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5386297945473011</v>
+        <v>0.5323666574014023</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2154427362448126</v>
+        <v>0.2169927362448126</v>
       </c>
       <c r="C88">
-        <v>-22.73267708456006</v>
+        <v>-23.39942978181299</v>
       </c>
       <c r="D88">
-        <v>18.41732291543994</v>
+        <v>18.25057021818701</v>
       </c>
       <c r="E88">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F88">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G88">
         <v>1.85</v>
@@ -8497,37 +8497,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M88">
-        <v>8.634399999999999</v>
+        <v>8.7348</v>
       </c>
       <c r="N88">
-        <v>-4.037733333333332</v>
+        <v>-4.138133333333332</v>
       </c>
       <c r="O88">
-        <v>-0.8883013333333331</v>
+        <v>-0.9103893333333332</v>
       </c>
       <c r="P88">
-        <v>-3.149431999999999</v>
+        <v>-3.227743999999999</v>
       </c>
       <c r="Q88">
-        <v>-1.829431999999999</v>
+        <v>-1.907743999999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4498576398438999</v>
+        <v>0.480938996754969</v>
       </c>
       <c r="T88">
-        <v>5.266225570182792</v>
+        <v>5.671319844812237</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1171206646283085</v>
+        <v>0.1157744500923509</v>
       </c>
       <c r="W88">
-        <v>0.1772821705426356</v>
+        <v>0.1775524904214559</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5323666574014023</v>
+        <v>0.5262475004197769</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2169927362448126</v>
+        <v>0.2185427362448126</v>
       </c>
       <c r="C89">
-        <v>-23.39942978181299</v>
+        <v>-24.06318997487893</v>
       </c>
       <c r="D89">
-        <v>18.25057021818701</v>
+        <v>18.08681002512106</v>
       </c>
       <c r="E89">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F89">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="G89">
         <v>1.85</v>
@@ -8579,37 +8579,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M89">
-        <v>8.7348</v>
+        <v>8.8352</v>
       </c>
       <c r="N89">
-        <v>-4.138133333333332</v>
+        <v>-4.238533333333333</v>
       </c>
       <c r="O89">
-        <v>-0.9103893333333332</v>
+        <v>-0.9324773333333333</v>
       </c>
       <c r="P89">
-        <v>-3.227743999999999</v>
+        <v>-3.306055999999999</v>
       </c>
       <c r="Q89">
-        <v>-1.907743999999999</v>
+        <v>-1.986056</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.480938996754969</v>
+        <v>0.5172005798178833</v>
       </c>
       <c r="T89">
-        <v>5.671319844812237</v>
+        <v>6.143929831879925</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1157744500923509</v>
+        <v>0.1144588313413015</v>
       </c>
       <c r="W89">
-        <v>0.1775524904214559</v>
+        <v>0.1778166666666667</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5262475004197769</v>
+        <v>0.520267415187734</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2185427362448126</v>
+        <v>0.2200927362448126</v>
       </c>
       <c r="C90">
-        <v>-24.06318997487893</v>
+        <v>-24.72403750153409</v>
       </c>
       <c r="D90">
-        <v>18.08681002512106</v>
+        <v>17.92596249846591</v>
       </c>
       <c r="E90">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="F90">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="G90">
         <v>1.85</v>
@@ -8661,37 +8661,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M90">
-        <v>8.8352</v>
+        <v>8.935600000000001</v>
       </c>
       <c r="N90">
-        <v>-4.238533333333333</v>
+        <v>-4.338933333333333</v>
       </c>
       <c r="O90">
-        <v>-0.9324773333333333</v>
+        <v>-0.9545653333333334</v>
       </c>
       <c r="P90">
-        <v>-3.306055999999999</v>
+        <v>-3.384368</v>
       </c>
       <c r="Q90">
-        <v>-1.986056</v>
+        <v>-2.064368</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5172005798178833</v>
+        <v>0.5600551779831453</v>
       </c>
       <c r="T90">
-        <v>6.143929831879925</v>
+        <v>6.702468907505372</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1144588313413015</v>
+        <v>0.1131727770565678</v>
       </c>
       <c r="W90">
-        <v>0.1778166666666667</v>
+        <v>0.1780749063670412</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.520267415187734</v>
+        <v>0.5144217138934898</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2200927362448126</v>
+        <v>0.2216427362448126</v>
       </c>
       <c r="C91">
-        <v>-24.72403750153409</v>
+        <v>-25.38204938457223</v>
       </c>
       <c r="D91">
-        <v>17.92596249846591</v>
+        <v>17.76795061542776</v>
       </c>
       <c r="E91">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="F91">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="G91">
         <v>1.85</v>
@@ -8743,37 +8743,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M91">
-        <v>8.935600000000001</v>
+        <v>9.036</v>
       </c>
       <c r="N91">
-        <v>-4.338933333333333</v>
+        <v>-4.439333333333332</v>
       </c>
       <c r="O91">
-        <v>-0.9545653333333334</v>
+        <v>-0.976653333333333</v>
       </c>
       <c r="P91">
-        <v>-3.384368</v>
+        <v>-3.462679999999999</v>
       </c>
       <c r="Q91">
-        <v>-2.064368</v>
+        <v>-2.142679999999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5600551779831453</v>
+        <v>0.6114806957814599</v>
       </c>
       <c r="T91">
-        <v>6.702468907505372</v>
+        <v>7.37271579825591</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1131727770565678</v>
+        <v>0.1119153017559392</v>
       </c>
       <c r="W91">
-        <v>0.1780749063670412</v>
+        <v>0.1783274074074074</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5144217138934898</v>
+        <v>0.5087059170724511</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2216427362448126</v>
+        <v>0.2231927362448126</v>
       </c>
       <c r="C92">
-        <v>-25.38204938457223</v>
+        <v>-26.0372999547867</v>
       </c>
       <c r="D92">
-        <v>17.76795061542776</v>
+        <v>17.61270004521329</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="F92">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="G92">
         <v>1.85</v>
@@ -8825,37 +8825,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M92">
-        <v>9.036</v>
+        <v>9.1364</v>
       </c>
       <c r="N92">
-        <v>-4.439333333333332</v>
+        <v>-4.539733333333333</v>
       </c>
       <c r="O92">
-        <v>-0.976653333333333</v>
+        <v>-0.9987413333333331</v>
       </c>
       <c r="P92">
-        <v>-3.462679999999999</v>
+        <v>-3.540991999999999</v>
       </c>
       <c r="Q92">
-        <v>-2.142679999999999</v>
+        <v>-2.220991999999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6114806957814599</v>
+        <v>0.6743341064238444</v>
       </c>
       <c r="T92">
-        <v>7.37271579825591</v>
+        <v>8.191906442506568</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1119153017559392</v>
+        <v>0.1106854632751047</v>
       </c>
       <c r="W92">
-        <v>0.1783274074074074</v>
+        <v>0.178574358974359</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5087059170724511</v>
+        <v>0.5031157421595669</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2231927362448126</v>
+        <v>0.2578831835538364</v>
       </c>
       <c r="C93">
-        <v>-26.0372999547867</v>
+        <v>-29.41820938216248</v>
       </c>
       <c r="D93">
-        <v>17.61270004521329</v>
+        <v>14.73179061783752</v>
       </c>
       <c r="E93">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="F93">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="G93">
         <v>1.85</v>
@@ -8907,45 +8907,45 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M93">
-        <v>9.1364</v>
+        <v>10.8468</v>
       </c>
       <c r="N93">
-        <v>-4.539733333333333</v>
+        <v>-6.250133333333332</v>
       </c>
       <c r="O93">
-        <v>-0.9987413333333331</v>
+        <v>-1.375029333333333</v>
       </c>
       <c r="P93">
-        <v>-3.540991999999999</v>
+        <v>-4.875103999999999</v>
       </c>
       <c r="Q93">
-        <v>-2.220991999999999</v>
+        <v>-3.555104</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6743341064238444</v>
+        <v>0.7646564610896227</v>
       </c>
       <c r="T93">
-        <v>8.191906442506568</v>
+        <v>9.369109511563256</v>
       </c>
       <c r="U93">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1106854632751047</v>
+        <v>0.09323179801108777</v>
       </c>
       <c r="W93">
-        <v>0.178574358974359</v>
+        <v>0.2138159420289855</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.5031157421595669</v>
+        <v>0.4237809000503989</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2578831835538364</v>
+        <v>0.2597831835538364</v>
       </c>
       <c r="C94">
-        <v>-29.41820938216248</v>
+        <v>-30.04901593298122</v>
       </c>
       <c r="D94">
-        <v>14.73179061783752</v>
+        <v>14.60098406701878</v>
       </c>
       <c r="E94">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="F94">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="G94">
         <v>1.85</v>
@@ -8989,37 +8989,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M94">
-        <v>10.8468</v>
+        <v>10.9647</v>
       </c>
       <c r="N94">
-        <v>-6.250133333333332</v>
+        <v>-6.368033333333333</v>
       </c>
       <c r="O94">
-        <v>-1.375029333333333</v>
+        <v>-1.400967333333333</v>
       </c>
       <c r="P94">
-        <v>-4.875103999999999</v>
+        <v>-4.967066</v>
       </c>
       <c r="Q94">
-        <v>-3.555104</v>
+        <v>-3.647066</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7646564610896227</v>
+        <v>0.8673502412452831</v>
       </c>
       <c r="T94">
-        <v>9.369109511563256</v>
+        <v>10.70755372750086</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09323179801108777</v>
+        <v>0.09222930555935564</v>
       </c>
       <c r="W94">
-        <v>0.2138159420289855</v>
+        <v>0.214052329749104</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4237809000503989</v>
+        <v>0.4192241161788893</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2597831835538364</v>
+        <v>0.2616831835538365</v>
       </c>
       <c r="C95">
-        <v>-30.04901593298122</v>
+        <v>-30.67752001222748</v>
       </c>
       <c r="D95">
-        <v>14.60098406701878</v>
+        <v>14.47247998777252</v>
       </c>
       <c r="E95">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="F95">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="G95">
         <v>1.85</v>
@@ -9071,37 +9071,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M95">
-        <v>10.9647</v>
+        <v>11.0826</v>
       </c>
       <c r="N95">
-        <v>-6.368033333333333</v>
+        <v>-6.485933333333334</v>
       </c>
       <c r="O95">
-        <v>-1.400967333333333</v>
+        <v>-1.426905333333333</v>
       </c>
       <c r="P95">
-        <v>-4.967066</v>
+        <v>-5.059028</v>
       </c>
       <c r="Q95">
-        <v>-3.647066</v>
+        <v>-3.739028</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8673502412452831</v>
+        <v>1.004275281452831</v>
       </c>
       <c r="T95">
-        <v>10.70755372750086</v>
+        <v>12.49214601541768</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09222930555935564</v>
+        <v>0.0912481427342561</v>
       </c>
       <c r="W95">
-        <v>0.214052329749104</v>
+        <v>0.2142836879432624</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4192241161788893</v>
+        <v>0.4147642851557096</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2616831835538365</v>
+        <v>0.2635831835538365</v>
       </c>
       <c r="C96">
-        <v>-30.67752001222748</v>
+        <v>-31.3037818820746</v>
       </c>
       <c r="D96">
-        <v>14.47247998777252</v>
+        <v>14.3462181179254</v>
       </c>
       <c r="E96">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="F96">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="G96">
         <v>1.85</v>
@@ -9153,37 +9153,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M96">
-        <v>11.0826</v>
+        <v>11.2005</v>
       </c>
       <c r="N96">
-        <v>-6.485933333333334</v>
+        <v>-6.603833333333332</v>
       </c>
       <c r="O96">
-        <v>-1.426905333333333</v>
+        <v>-1.452843333333333</v>
       </c>
       <c r="P96">
-        <v>-5.059028</v>
+        <v>-5.150989999999999</v>
       </c>
       <c r="Q96">
-        <v>-3.739028</v>
+        <v>-3.830989999999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.004275281452831</v>
+        <v>1.195970337743397</v>
       </c>
       <c r="T96">
-        <v>12.49214601541768</v>
+        <v>14.99057521850122</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0912481427342561</v>
+        <v>0.09028763596863237</v>
       </c>
       <c r="W96">
-        <v>0.2142836879432624</v>
+        <v>0.2145101754385965</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4147642851557096</v>
+        <v>0.4103983453119653</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2635831835538365</v>
+        <v>0.2654831835538365</v>
       </c>
       <c r="C97">
-        <v>-31.3037818820746</v>
+        <v>-31.92785971990956</v>
       </c>
       <c r="D97">
-        <v>14.3462181179254</v>
+        <v>14.22214028009044</v>
       </c>
       <c r="E97">
-        <v>12.5</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="F97">
-        <v>47.5</v>
+        <v>48.00000000000001</v>
       </c>
       <c r="G97">
         <v>1.85</v>
@@ -9235,37 +9235,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M97">
-        <v>11.2005</v>
+        <v>11.3184</v>
       </c>
       <c r="N97">
-        <v>-6.603833333333332</v>
+        <v>-6.721733333333335</v>
       </c>
       <c r="O97">
-        <v>-1.452843333333333</v>
+        <v>-1.478781333333334</v>
       </c>
       <c r="P97">
-        <v>-5.150989999999999</v>
+        <v>-5.242952000000001</v>
       </c>
       <c r="Q97">
-        <v>-3.830989999999999</v>
+        <v>-3.922952000000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.195970337743397</v>
+        <v>1.483512922179248</v>
       </c>
       <c r="T97">
-        <v>14.99057521850122</v>
+        <v>18.73821902312654</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09028763596863237</v>
+        <v>0.08934713976062576</v>
       </c>
       <c r="W97">
-        <v>0.2145101754385965</v>
+        <v>0.2147319444444444</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4103983453119653</v>
+        <v>0.4061233625482989</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2654831835538364</v>
+        <v>0.2673831835538364</v>
       </c>
       <c r="C98">
-        <v>-31.92785971990955</v>
+        <v>-32.5498097077145</v>
       </c>
       <c r="D98">
-        <v>14.22214028009045</v>
+        <v>14.1001902922855</v>
       </c>
       <c r="E98">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="F98">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="G98">
         <v>1.85</v>
@@ -9317,37 +9317,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M98">
-        <v>11.3184</v>
+        <v>11.4363</v>
       </c>
       <c r="N98">
-        <v>-6.721733333333333</v>
+        <v>-6.839633333333333</v>
       </c>
       <c r="O98">
-        <v>-1.478781333333333</v>
+        <v>-1.504719333333333</v>
       </c>
       <c r="P98">
-        <v>-5.242952</v>
+        <v>-5.334914</v>
       </c>
       <c r="Q98">
-        <v>-3.922952</v>
+        <v>-4.014914000000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.483512922179244</v>
+        <v>1.962750562905659</v>
       </c>
       <c r="T98">
-        <v>18.73821902312649</v>
+        <v>24.98429203083532</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08934713976062578</v>
+        <v>0.08842603522701108</v>
       </c>
       <c r="W98">
-        <v>0.2147319444444444</v>
+        <v>0.2149491408934708</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4061233625482989</v>
+        <v>0.4019365237591412</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2673831835538364</v>
+        <v>0.2692831835538364</v>
       </c>
       <c r="C99">
-        <v>-32.5498097077145</v>
+        <v>-33.1696861168891</v>
       </c>
       <c r="D99">
-        <v>14.1001902922855</v>
+        <v>13.9803138831109</v>
       </c>
       <c r="E99">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="F99">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="G99">
         <v>1.85</v>
@@ -9399,37 +9399,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M99">
-        <v>11.4363</v>
+        <v>11.5542</v>
       </c>
       <c r="N99">
-        <v>-6.839633333333333</v>
+        <v>-6.957533333333332</v>
       </c>
       <c r="O99">
-        <v>-1.504719333333333</v>
+        <v>-1.530657333333333</v>
       </c>
       <c r="P99">
-        <v>-5.334914</v>
+        <v>-5.426875999999999</v>
       </c>
       <c r="Q99">
-        <v>-4.014914000000001</v>
+        <v>-4.106876</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.962750562905659</v>
+        <v>2.921225844358487</v>
       </c>
       <c r="T99">
-        <v>24.98429203083532</v>
+        <v>37.47643804625297</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08842603522701108</v>
+        <v>0.08752372874510281</v>
       </c>
       <c r="W99">
-        <v>0.2149491408934708</v>
+        <v>0.2151619047619047</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4019365237591412</v>
+        <v>0.3978351306595582</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2692831835538364</v>
+        <v>0.2711831835538365</v>
       </c>
       <c r="C100">
-        <v>-33.1696861168891</v>
+        <v>-33.78754138878239</v>
       </c>
       <c r="D100">
-        <v>13.9803138831109</v>
+        <v>13.86245861121762</v>
       </c>
       <c r="E100">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="F100">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="G100">
         <v>1.85</v>
@@ -9481,37 +9481,37 @@
         <v>4.596666666666668</v>
       </c>
       <c r="M100">
-        <v>11.5542</v>
+        <v>11.6721</v>
       </c>
       <c r="N100">
-        <v>-6.957533333333332</v>
+        <v>-7.075433333333333</v>
       </c>
       <c r="O100">
-        <v>-1.530657333333333</v>
+        <v>-1.556595333333333</v>
       </c>
       <c r="P100">
-        <v>-5.426875999999999</v>
+        <v>-5.518838</v>
       </c>
       <c r="Q100">
-        <v>-4.106876</v>
+        <v>-4.198838</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.921225844358487</v>
+        <v>5.796651688716975</v>
       </c>
       <c r="T100">
-        <v>37.47643804625297</v>
+        <v>74.95287609250595</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08752372874510281</v>
+        <v>0.08663965067697045</v>
       </c>
       <c r="W100">
-        <v>0.2151619047619047</v>
+        <v>0.2153703703703704</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3978351306595582</v>
+        <v>0.3938165939862294</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2711831835538365</v>
-      </c>
-      <c r="C101">
-        <v>-33.78754138878239</v>
-      </c>
-      <c r="D101">
-        <v>13.86245861121762</v>
-      </c>
-      <c r="E101">
-        <v>14.5</v>
-      </c>
-      <c r="F101">
-        <v>49.5</v>
-      </c>
-      <c r="G101">
-        <v>1.85</v>
-      </c>
-      <c r="H101">
-        <v>15</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="K101">
-        <v>1.32</v>
-      </c>
-      <c r="L101">
-        <v>4.596666666666668</v>
-      </c>
-      <c r="M101">
-        <v>11.6721</v>
-      </c>
-      <c r="N101">
-        <v>-7.075433333333333</v>
-      </c>
-      <c r="O101">
-        <v>-1.556595333333333</v>
-      </c>
-      <c r="P101">
-        <v>-5.518838</v>
-      </c>
-      <c r="Q101">
-        <v>-4.198838</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.796651688716975</v>
-      </c>
-      <c r="T101">
-        <v>74.95287609250595</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08663965067697045</v>
-      </c>
-      <c r="W101">
-        <v>0.2153703703703704</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3938165939862294</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
